--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3E8774D-3928-4D55-9237-DEEF8C9FDB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87420BCE-40CA-4707-925E-ADA7A23753CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12735" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1110" windowWidth="13035" windowHeight="16890" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <sheet name="TTS-motorbikes-psgr" sheetId="17" r:id="rId20"/>
     <sheet name="TTS-motorbikes-frgt" sheetId="18" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6411,9 +6411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6451,9 +6451,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6486,26 +6486,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6538,26 +6521,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6745,7 +6711,7 @@
         <v>987</v>
       </c>
       <c r="C1" s="48">
-        <v>44907</v>
+        <v>45258</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -10822,97 +10788,97 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="K4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Z4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AB4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AC4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\TTS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1690D90-B88A-4916-A6CE-CC1A8F7A5860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E57D70B5-3EB4-4444-9025-E3D64D8E96F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="19560" windowHeight="17085" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1001">
   <si>
     <t>Source:</t>
   </si>
@@ -3051,6 +3051,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
   </si>
 </sst>
 </file>
@@ -3849,7 +3852,7 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3925,6 +3928,7 @@
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="88">
     <cellStyle name="20% - Accent1" xfId="28" builtinId="30" customBuiltin="1"/>
@@ -7408,18 +7412,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B130"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C130"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="56.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>905</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1" s="49">
+        <v>45310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -7427,512 +7437,512 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="12" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="31"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="31" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="3">
         <v>2020</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" s="13" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" s="3">
         <v>2014</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="31" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>33</v>
       </c>
       <c r="B61" s="14"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B63" s="12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B76" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B93" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="125" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>55</v>
       </c>
@@ -7952,13 +7962,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -8082,7 +8092,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8207,7 +8217,7 @@
         <v>0.99913267926293059</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8332,7 +8342,7 @@
         <v>1.2225974073810479E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8457,7 +8467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8582,7 +8592,7 @@
         <v>3.0818463927506201E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8707,7 +8717,7 @@
         <v>4.9982798179070587E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -8832,7 +8842,7 @@
         <v>8.6165104068937348E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -8968,12 +8978,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -9098,7 +9108,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -9223,7 +9233,7 @@
         <v>0.99967234626801127</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -9348,7 +9358,7 @@
         <v>1.2353695258898144E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9473,7 +9483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9598,7 +9608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9723,7 +9733,7 @@
         <v>4.9265458207603127E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -9848,7 +9858,7 @@
         <v>8.6165104068937001E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -9984,12 +9994,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -10114,7 +10124,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -10239,257 +10249,257 @@
         <v>0.9996355795222398</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
         <f>Data!I25</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="C3">
         <f>Data!J25</f>
-        <v>0.30043157833481504</v>
+        <v>0.29596244960239987</v>
       </c>
       <c r="D3">
         <f>Data!K25</f>
-        <v>0.2997017384509349</v>
+        <v>0.29525559107671612</v>
       </c>
       <c r="E3">
         <f>Data!L25</f>
-        <v>0.29872838007535607</v>
+        <v>0.29431288202296346</v>
       </c>
       <c r="F3">
         <f>Data!M25</f>
-        <v>0.29743557082505373</v>
+        <v>0.2930607810336332</v>
       </c>
       <c r="G3">
         <f>Data!N25</f>
-        <v>0.29572780273850224</v>
+        <v>0.29140678752282123</v>
       </c>
       <c r="H3">
         <f>Data!O25</f>
-        <v>0.29348805553810225</v>
+        <v>0.28923756597307232</v>
       </c>
       <c r="I3">
         <f>Data!P25</f>
-        <v>0.29057816867446151</v>
+        <v>0.28641930626464923</v>
       </c>
       <c r="J3">
         <f>Data!Q25</f>
-        <v>0.28684357792599674</v>
+        <v>0.28280231112804816</v>
       </c>
       <c r="K3">
         <f>Data!R25</f>
-        <v>0.28212505041848135</v>
+        <v>0.27823236164867954</v>
       </c>
       <c r="L3">
         <f>Data!S25</f>
-        <v>0.27627995437001424</v>
+        <v>0.2725713172654462</v>
       </c>
       <c r="M3">
         <f>Data!T25</f>
-        <v>0.26921392877955547</v>
+        <v>0.26572778823718668</v>
       </c>
       <c r="N3">
         <f>Data!U25</f>
-        <v>0.26091971966867544</v>
+        <v>0.25769474900033379</v>
       </c>
       <c r="O3">
         <f>Data!V25</f>
-        <v>0.25151367915559786</v>
+        <v>0.24858488795211589</v>
       </c>
       <c r="P3">
         <f>Data!W25</f>
-        <v>0.24125472684112267</v>
+        <v>0.23864897177620478</v>
       </c>
       <c r="Q3">
         <f>Data!X25</f>
-        <v>0.23053064887219032</v>
+        <v>0.22826257592436899</v>
       </c>
       <c r="R3">
         <f>Data!Y25</f>
-        <v>0.219806570903258</v>
+        <v>0.21787618007253318</v>
       </c>
       <c r="S3">
         <f>Data!Z25</f>
-        <v>0.20954761858878282</v>
+        <v>0.20794026389662207</v>
       </c>
       <c r="T3">
         <f>Data!AA25</f>
-        <v>0.20014157807570523</v>
+        <v>0.19883040284840414</v>
       </c>
       <c r="U3">
         <f>Data!AB25</f>
-        <v>0.19184736896482521</v>
+        <v>0.19079736361155128</v>
       </c>
       <c r="V3">
         <f>Data!AC25</f>
-        <v>0.18478134337436644</v>
+        <v>0.18395383458329176</v>
       </c>
       <c r="W3">
         <f>Data!AD25</f>
-        <v>0.1789362473258993</v>
+        <v>0.17829279020005839</v>
       </c>
       <c r="X3">
         <f>Data!AE25</f>
-        <v>0.17421771981838394</v>
+        <v>0.17372284072068978</v>
       </c>
       <c r="Y3">
         <f>Data!AF25</f>
-        <v>0.17048312906991916</v>
+        <v>0.17010584558408873</v>
       </c>
       <c r="Z3">
         <f>Data!AG25</f>
-        <v>0.16757324220627842</v>
+        <v>0.16728758587566564</v>
       </c>
       <c r="AA3">
         <f>Data!AH25</f>
-        <v>0.16533349500587841</v>
+        <v>0.1651183643259167</v>
       </c>
       <c r="AB3">
         <f>Data!AI25</f>
-        <v>0.16362572691932695</v>
+        <v>0.16346437081510473</v>
       </c>
       <c r="AC3">
         <f>Data!AJ25</f>
-        <v>0.16233291766902463</v>
+        <v>0.1622122698257745</v>
       </c>
       <c r="AD3">
         <f>Data!AK25</f>
-        <v>0.16135955929344575</v>
+        <v>0.16126956077202181</v>
       </c>
       <c r="AE3">
         <f>Data!AL25</f>
-        <v>0.16062971940956564</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.16056270224633809</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
         <f>Data!I26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="C4">
         <f>Data!J26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="D4">
         <f>Data!K26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="E4">
         <f>Data!L26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="F4">
         <f>Data!M26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="G4">
         <f>Data!N26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="H4">
         <f>Data!O26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="I4">
         <f>Data!P26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="J4">
         <f>Data!Q26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="K4">
         <f>Data!R26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="L4">
         <f>Data!S26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="M4">
         <f>Data!T26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="N4">
         <f>Data!U26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="O4">
         <f>Data!V26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="P4">
         <f>Data!W26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Q4">
         <f>Data!X26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="R4">
         <f>Data!Y26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="S4">
         <f>Data!Z26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="T4">
         <f>Data!AA26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="U4">
         <f>Data!AB26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="V4">
         <f>Data!AC26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="W4">
         <f>Data!AD26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="X4">
         <f>Data!AE26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Y4">
         <f>Data!AF26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Z4">
         <f>Data!AG26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AA4">
         <f>Data!AH26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AB4">
         <f>Data!AI26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AC4">
         <f>Data!AJ26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AD4">
         <f>Data!AK26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AE4">
         <f>Data!AL26</f>
-        <v>0.30255990331064825</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.29802375741500553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -10614,7 +10624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -10739,254 +10749,254 @@
         <v>5.9113558098403615E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
       <c r="B7">
         <f>Data!I29</f>
-        <v>2.1823637453696615E-2</v>
+        <v>2.1496445375763083E-2</v>
       </c>
       <c r="C7">
         <f>Data!J29</f>
-        <v>2.1823637453692868E-2</v>
+        <v>2.1496445375760231E-2</v>
       </c>
       <c r="D7">
         <f>Data!K29</f>
-        <v>4.0415167611165259E-2</v>
+        <v>3.9809241000682505E-2</v>
       </c>
       <c r="E7">
         <f>Data!L29</f>
-        <v>5.900669776863765E-2</v>
+        <v>5.8122036625604778E-2</v>
       </c>
       <c r="F7">
         <f>Data!M29</f>
-        <v>7.7598227926110042E-2</v>
+        <v>7.6434832250534157E-2</v>
       </c>
       <c r="G7">
         <f>Data!N29</f>
-        <v>9.6189758083582433E-2</v>
+        <v>9.4747627875456431E-2</v>
       </c>
       <c r="H7">
         <f>Data!O29</f>
-        <v>0.11478128824105482</v>
+        <v>0.1130604235003787</v>
       </c>
       <c r="I7">
         <f>Data!P29</f>
-        <v>0.13337281839852722</v>
+        <v>0.13137321912530098</v>
       </c>
       <c r="J7">
         <f>Data!Q29</f>
-        <v>0.15196434855599961</v>
+        <v>0.14968601475022325</v>
       </c>
       <c r="K7">
         <f>Data!R29</f>
-        <v>0.170555878713472</v>
+        <v>0.16799881037514552</v>
       </c>
       <c r="L7">
         <f>Data!S29</f>
-        <v>0.18914740887094439</v>
+        <v>0.1863116060000678</v>
       </c>
       <c r="M7">
         <f>Data!T29</f>
-        <v>0.20773893902841678</v>
+        <v>0.20462440162499007</v>
       </c>
       <c r="N7">
         <f>Data!U29</f>
-        <v>0.22633046918588917</v>
+        <v>0.22293719724991234</v>
       </c>
       <c r="O7">
         <f>Data!V29</f>
-        <v>0.24492199934336156</v>
+        <v>0.24124999287483462</v>
       </c>
       <c r="P7">
         <f>Data!W29</f>
-        <v>0.26351352950083395</v>
+        <v>0.25956278849975689</v>
       </c>
       <c r="Q7">
         <f>Data!X29</f>
-        <v>0.28210505965830635</v>
+        <v>0.27787558412467916</v>
       </c>
       <c r="R7">
         <f>Data!Y29</f>
-        <v>0.30069658981577874</v>
+        <v>0.29618837974960144</v>
       </c>
       <c r="S7">
         <f>Data!Z29</f>
-        <v>0.31928811997325113</v>
+        <v>0.31450117537452371</v>
       </c>
       <c r="T7">
         <f>Data!AA29</f>
-        <v>0.33787965013072352</v>
+        <v>0.33281397099944598</v>
       </c>
       <c r="U7">
         <f>Data!AB29</f>
-        <v>0.35647118028819591</v>
+        <v>0.35112676662436826</v>
       </c>
       <c r="V7">
         <f>Data!AC29</f>
-        <v>0.3750627104456683</v>
+        <v>0.36943956224929764</v>
       </c>
       <c r="W7">
         <f>Data!AD29</f>
-        <v>0.39365424060314069</v>
+        <v>0.38775235787421991</v>
       </c>
       <c r="X7">
         <f>Data!AE29</f>
-        <v>0.41224577076061308</v>
+        <v>0.40606515349914218</v>
       </c>
       <c r="Y7">
         <f>Data!AF29</f>
-        <v>0.43083730091808548</v>
+        <v>0.42437794912406446</v>
       </c>
       <c r="Z7">
         <f>Data!AG29</f>
-        <v>0.44942883107555787</v>
+        <v>0.44269074474898673</v>
       </c>
       <c r="AA7">
         <f>Data!AH29</f>
-        <v>0.46802036123303026</v>
+        <v>0.461003540373909</v>
       </c>
       <c r="AB7">
         <f>Data!AI29</f>
-        <v>0.48661189139050265</v>
+        <v>0.47931633599883128</v>
       </c>
       <c r="AC7">
         <f>Data!AJ29</f>
-        <v>0.50520342154797504</v>
+        <v>0.49762913162375355</v>
       </c>
       <c r="AD7">
         <f>Data!AK29</f>
-        <v>0.52379495170544743</v>
+        <v>0.51594192724867582</v>
       </c>
       <c r="AE7">
         <f>Data!AL29</f>
-        <v>0.54238648186291982</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.5342547228735981</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
       <c r="B8">
         <f>Data!I30</f>
-        <v>8.5993749223261043E-5</v>
+        <v>8.470448323552864E-5</v>
       </c>
       <c r="C8">
         <f>Data!J30</f>
-        <v>8.2342485951046606E-4</v>
+        <v>8.2215464117929744E-4</v>
       </c>
       <c r="D8">
         <f>Data!K30</f>
-        <v>1.0763028936513275E-3</v>
+        <v>1.0750392070949643E-3</v>
       </c>
       <c r="E8">
         <f>Data!L30</f>
-        <v>1.4135562528708127E-3</v>
+        <v>1.4123012774822749E-3</v>
       </c>
       <c r="F8">
         <f>Data!M30</f>
-        <v>1.861494312925186E-3</v>
+        <v>1.860250907661926E-3</v>
       </c>
       <c r="G8">
         <f>Data!N30</f>
-        <v>2.4532090794568743E-3</v>
+        <v>2.4519809580343683E-3</v>
       </c>
       <c r="H8">
         <f>Data!O30</f>
-        <v>3.229246237084574E-3</v>
+        <v>3.2280381605029394E-3</v>
       </c>
       <c r="I8">
         <f>Data!P30</f>
-        <v>4.2374762419148592E-3</v>
+        <v>4.2362942076558247E-3</v>
       </c>
       <c r="J8">
         <f>Data!Q30</f>
-        <v>5.5314531643209574E-3</v>
+        <v>5.530304553154162E-3</v>
       </c>
       <c r="K8">
         <f>Data!R30</f>
-        <v>7.1663486893455471E-3</v>
+        <v>7.1652423071111148E-3</v>
       </c>
       <c r="L8">
         <f>Data!S30</f>
-        <v>9.1915824847949544E-3</v>
+        <v>9.1905284138303605E-3</v>
       </c>
       <c r="M8">
         <f>Data!T30</f>
-        <v>1.1639849152553195E-2</v>
+        <v>1.1638858319689102E-2</v>
       </c>
       <c r="N8">
         <f>Data!U30</f>
-        <v>1.4513662081988942E-2</v>
+        <v>1.4512745478976212E-2</v>
       </c>
       <c r="O8">
         <f>Data!V30</f>
-        <v>1.7772707095192228E-2</v>
+        <v>1.7771874672476845E-2</v>
       </c>
       <c r="P8">
         <f>Data!W30</f>
-        <v>2.1327272625150932E-2</v>
+        <v>2.1326532015952099E-2</v>
       </c>
       <c r="Q8">
         <f>Data!X30</f>
-        <v>2.5042996874611631E-2</v>
+        <v>2.5042352241617768E-2</v>
       </c>
       <c r="R8">
         <f>Data!Y30</f>
-        <v>2.8758721124072337E-2</v>
+        <v>2.8758172467283436E-2</v>
       </c>
       <c r="S8">
         <f>Data!Z30</f>
-        <v>3.2313286654031034E-2</v>
+        <v>3.2312829810758684E-2</v>
       </c>
       <c r="T8">
         <f>Data!AA30</f>
-        <v>3.5572331667234322E-2</v>
+        <v>3.5571959004259315E-2</v>
       </c>
       <c r="U8">
         <f>Data!AB30</f>
-        <v>3.8446144596670069E-2</v>
+        <v>3.8445846163546425E-2</v>
       </c>
       <c r="V8">
         <f>Data!AC30</f>
-        <v>4.0894411264428311E-2</v>
+        <v>4.0894176069405173E-2</v>
       </c>
       <c r="W8">
         <f>Data!AD30</f>
-        <v>4.291964505987772E-2</v>
+        <v>4.2919462176124419E-2</v>
       </c>
       <c r="X8">
         <f>Data!AE30</f>
-        <v>4.4554540584902311E-2</v>
+        <v>4.4554399930081368E-2</v>
       </c>
       <c r="Y8">
         <f>Data!AF30</f>
-        <v>4.5848517507308409E-2</v>
+        <v>4.5848410275579711E-2</v>
       </c>
       <c r="Z8">
         <f>Data!AG30</f>
-        <v>4.685674751213869E-2</v>
+        <v>4.6856666322732596E-2</v>
       </c>
       <c r="AA8">
         <f>Data!AH30</f>
-        <v>4.7632784669766393E-2</v>
+        <v>4.7632723525201169E-2</v>
       </c>
       <c r="AB8">
         <f>Data!AI30</f>
-        <v>4.8224499436298078E-2</v>
+        <v>4.822445357557361E-2</v>
       </c>
       <c r="AC8">
         <f>Data!AJ30</f>
-        <v>4.8672437496352451E-2</v>
+        <v>4.8672403205753251E-2</v>
       </c>
       <c r="AD8">
         <f>Data!AK30</f>
-        <v>4.9009690855571941E-2</v>
+        <v>4.900966527614057E-2</v>
       </c>
       <c r="AE8">
         <f>Data!AL30</f>
-        <v>4.9262568889712796E-2</v>
+        <v>4.9262549842056233E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11000,12 +11010,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -11130,7 +11140,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -11255,7 +11265,7 @@
         <v>0.99924940887163149</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11380,7 +11390,7 @@
         <v>5.2146832307325378E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11505,7 +11515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11630,7 +11640,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -11755,7 +11765,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -11880,7 +11890,7 @@
         <v>6.1785980743152003E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12016,12 +12026,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -12146,7 +12156,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -12271,7 +12281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12396,7 +12406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12521,7 +12531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12646,7 +12656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12771,7 +12781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -12896,7 +12906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -13032,12 +13042,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -13162,7 +13172,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -13287,7 +13297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13412,7 +13422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13537,7 +13547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13662,7 +13672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13787,7 +13797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13912,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -14048,12 +14058,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -14178,132 +14188,132 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
         <f>Data!I52</f>
-        <v>0.75216927859794647</v>
+        <v>0.93664816809218165</v>
       </c>
       <c r="C2">
         <f>Data!J52</f>
-        <v>0.75583073753050711</v>
+        <v>0.93758413006461472</v>
       </c>
       <c r="D2">
         <f>Data!K52</f>
-        <v>0.75708631588086017</v>
+        <v>0.93790508780604664</v>
       </c>
       <c r="E2">
         <f>Data!L52</f>
-        <v>0.75876083070322697</v>
+        <v>0.93833313635851656</v>
       </c>
       <c r="F2">
         <f>Data!M52</f>
-        <v>0.76098491209651287</v>
+        <v>0.93890166809574294</v>
       </c>
       <c r="G2">
         <f>Data!N52</f>
-        <v>0.76392286696066514</v>
+        <v>0.93965268403780833</v>
       </c>
       <c r="H2">
         <f>Data!O52</f>
-        <v>0.76777601085866032</v>
+        <v>0.94063764555977569</v>
       </c>
       <c r="I2">
         <f>Data!P52</f>
-        <v>0.77278202797098927</v>
+        <v>0.94191731077978458</v>
       </c>
       <c r="J2">
         <f>Data!Q52</f>
-        <v>0.77920682249752604</v>
+        <v>0.94355965157024346</v>
       </c>
       <c r="K2">
         <f>Data!R52</f>
-        <v>0.78732433034388383</v>
+        <v>0.94563469291170243</v>
       </c>
       <c r="L2">
         <f>Data!S52</f>
-        <v>0.79737992776502331</v>
+        <v>0.94820515921205761</v>
       </c>
       <c r="M2">
         <f>Data!T52</f>
-        <v>0.80953594849008148</v>
+        <v>0.95131254709877777</v>
       </c>
       <c r="N2">
         <f>Data!U52</f>
-        <v>0.82380487188401408</v>
+        <v>0.95496004661475364</v>
       </c>
       <c r="O2">
         <f>Data!V52</f>
-        <v>0.83998653185027594</v>
+        <v>0.95909649021776056</v>
       </c>
       <c r="P2">
         <f>Data!W52</f>
-        <v>0.8576354966545553</v>
+        <v>0.96360801423424369</v>
       </c>
       <c r="Q2">
         <f>Data!X52</f>
-        <v>0.87608463929897318</v>
+        <v>0.96832408404609083</v>
       </c>
       <c r="R2">
         <f>Data!Y52</f>
-        <v>0.89453378194339117</v>
+        <v>0.97304015385793796</v>
       </c>
       <c r="S2">
         <f>Data!Z52</f>
-        <v>0.91218274674767053</v>
+        <v>0.9775516778744211</v>
       </c>
       <c r="T2">
         <f>Data!AA52</f>
-        <v>0.92836440671393228</v>
+        <v>0.98168812147742801</v>
       </c>
       <c r="U2">
         <f>Data!AB52</f>
-        <v>0.94263333010786499</v>
+        <v>0.98533562099340388</v>
       </c>
       <c r="V2">
         <f>Data!AC52</f>
-        <v>0.95478935083292327</v>
+        <v>0.98844300888012404</v>
       </c>
       <c r="W2">
         <f>Data!AD52</f>
-        <v>0.96484494825406264</v>
+        <v>0.99101347518047922</v>
       </c>
       <c r="X2">
         <f>Data!AE52</f>
-        <v>0.97296245610042043</v>
+        <v>0.99308851652193819</v>
       </c>
       <c r="Y2">
         <f>Data!AF52</f>
-        <v>0.9793872506269572</v>
+        <v>0.99473085731239708</v>
       </c>
       <c r="Z2">
         <f>Data!AG52</f>
-        <v>0.98439326773928615</v>
+        <v>0.99601052253240596</v>
       </c>
       <c r="AA2">
         <f>Data!AH52</f>
-        <v>0.98824641163728133</v>
+        <v>0.99699548405437333</v>
       </c>
       <c r="AB2">
         <f>Data!AI52</f>
-        <v>0.9911843665014336</v>
+        <v>0.99774649999643872</v>
       </c>
       <c r="AC2">
         <f>Data!AJ52</f>
-        <v>0.99340844789471949</v>
+        <v>0.99831503173366509</v>
       </c>
       <c r="AD2">
         <f>Data!AK52</f>
-        <v>0.99508296271708629</v>
+        <v>0.99874308028613501</v>
       </c>
       <c r="AE2">
         <f>Data!AL52</f>
-        <v>0.99633854106743935</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+        <v>0.99906403802756694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14428,7 +14438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14553,132 +14563,132 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <f>Data!I55</f>
-        <v>0.24783072140205353</v>
+        <v>6.3351831907818346E-2</v>
       </c>
       <c r="C5">
         <f>Data!J55</f>
-        <v>0.2478307214020532</v>
+        <v>6.3351831907809242E-2</v>
       </c>
       <c r="D5">
         <f>Data!K55</f>
-        <v>0.27469390992341403</v>
+        <v>9.6803552196817577E-2</v>
       </c>
       <c r="E5">
         <f>Data!L55</f>
-        <v>0.30155709844476775</v>
+        <v>0.13025527248582591</v>
       </c>
       <c r="F5">
         <f>Data!M55</f>
-        <v>0.32842028696612147</v>
+        <v>0.16370699277483425</v>
       </c>
       <c r="G5">
         <f>Data!N55</f>
-        <v>0.35528347548747519</v>
+        <v>0.19715871306384258</v>
       </c>
       <c r="H5">
         <f>Data!O55</f>
-        <v>0.38214666400883601</v>
+        <v>0.23061043335285092</v>
       </c>
       <c r="I5">
         <f>Data!P55</f>
-        <v>0.40900985253018973</v>
+        <v>0.26406215364185925</v>
       </c>
       <c r="J5">
         <f>Data!Q55</f>
-        <v>0.43587304105154345</v>
+        <v>0.29751387393085338</v>
       </c>
       <c r="K5">
         <f>Data!R55</f>
-        <v>0.46273622957289717</v>
+        <v>0.33096559421986171</v>
       </c>
       <c r="L5">
         <f>Data!S55</f>
-        <v>0.48959941809425089</v>
+        <v>0.36441731450887005</v>
       </c>
       <c r="M5">
         <f>Data!T55</f>
-        <v>0.51646260661561172</v>
+        <v>0.39786903479787838</v>
       </c>
       <c r="N5">
         <f>Data!U55</f>
-        <v>0.54332579513696544</v>
+        <v>0.43132075508688672</v>
       </c>
       <c r="O5">
         <f>Data!V55</f>
-        <v>0.57018898365831916</v>
+        <v>0.46477247537589506</v>
       </c>
       <c r="P5">
         <f>Data!W55</f>
-        <v>0.59705217217967288</v>
+        <v>0.49822419566490339</v>
       </c>
       <c r="Q5">
         <f>Data!X55</f>
-        <v>0.6239153607010266</v>
+        <v>0.53167591595391173</v>
       </c>
       <c r="R5">
         <f>Data!Y55</f>
-        <v>0.65077854922238743</v>
+        <v>0.56512763624290585</v>
       </c>
       <c r="S5">
         <f>Data!Z55</f>
-        <v>0.67764173774374115</v>
+        <v>0.59857935653191419</v>
       </c>
       <c r="T5">
         <f>Data!AA55</f>
-        <v>0.70450492626509487</v>
+        <v>0.63203107682092252</v>
       </c>
       <c r="U5">
         <f>Data!AB55</f>
-        <v>0.73136811478644859</v>
+        <v>0.66548279710993086</v>
       </c>
       <c r="V5">
         <f>Data!AC55</f>
-        <v>0.75823130330780941</v>
+        <v>0.69893451739893919</v>
       </c>
       <c r="W5">
         <f>Data!AD55</f>
-        <v>0.78509449182916313</v>
+        <v>0.73238623768794753</v>
       </c>
       <c r="X5">
         <f>Data!AE55</f>
-        <v>0.81195768035051685</v>
+        <v>0.76583795797695586</v>
       </c>
       <c r="Y5">
         <f>Data!AF55</f>
-        <v>0.83882086887187057</v>
+        <v>0.7992896782659642</v>
       </c>
       <c r="Z5">
         <f>Data!AG55</f>
-        <v>0.86568405739322429</v>
+        <v>0.83274139855495832</v>
       </c>
       <c r="AA5">
         <f>Data!AH55</f>
-        <v>0.89254724591458512</v>
+        <v>0.86619311884396666</v>
       </c>
       <c r="AB5">
         <f>Data!AI55</f>
-        <v>0.91941043443593884</v>
+        <v>0.89964483913297499</v>
       </c>
       <c r="AC5">
         <f>Data!AJ55</f>
-        <v>0.94627362295729256</v>
+        <v>0.93309655942198333</v>
       </c>
       <c r="AD5">
         <f>Data!AK55</f>
-        <v>0.97313681147864628</v>
+        <v>0.96654827971099166</v>
       </c>
       <c r="AE5">
         <f>Data!AL55</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -14803,7 +14813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -14928,7 +14938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -15064,12 +15074,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -15194,7 +15204,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -15319,7 +15329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -15444,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -15569,7 +15579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -15694,7 +15704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15819,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -15944,7 +15954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16080,12 +16090,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -16210,7 +16220,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -16335,7 +16345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -16460,7 +16470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -16585,7 +16595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -16710,7 +16720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16835,7 +16845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -16960,7 +16970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -17096,12 +17106,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -17226,7 +17236,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17351,7 +17361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17476,7 +17486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -17601,7 +17611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -17726,7 +17736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -17851,7 +17861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -17976,7 +17986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -18109,9 +18119,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AJ76"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -18209,27 +18219,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>147</v>
       </c>
@@ -18336,7 +18346,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>151</v>
       </c>
@@ -18344,7 +18354,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -18352,7 +18362,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -18462,7 +18472,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -18572,7 +18582,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -18682,7 +18692,7 @@
         <v>-1E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>165</v>
       </c>
@@ -18690,7 +18700,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -18800,7 +18810,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -18910,7 +18920,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -19020,7 +19030,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>176</v>
       </c>
@@ -19130,7 +19140,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>179</v>
       </c>
@@ -19240,7 +19250,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>182</v>
       </c>
@@ -19350,7 +19360,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>185</v>
       </c>
@@ -19460,7 +19470,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -19570,7 +19580,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>191</v>
       </c>
@@ -19680,7 +19690,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -19790,7 +19800,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -19900,7 +19910,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -20010,7 +20020,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -20120,7 +20130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -20230,7 +20240,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -20340,7 +20350,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -20450,7 +20460,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>114</v>
       </c>
@@ -20560,7 +20570,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>216</v>
       </c>
@@ -20568,7 +20578,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>218</v>
       </c>
@@ -20576,7 +20586,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>155</v>
       </c>
@@ -20686,7 +20696,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>159</v>
       </c>
@@ -20796,7 +20806,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>224</v>
       </c>
@@ -20906,7 +20916,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>227</v>
       </c>
@@ -20914,7 +20924,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>167</v>
       </c>
@@ -21024,7 +21034,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>170</v>
       </c>
@@ -21134,7 +21144,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>173</v>
       </c>
@@ -21244,7 +21254,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>176</v>
       </c>
@@ -21354,7 +21364,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>179</v>
       </c>
@@ -21464,7 +21474,7 @@
         <v>9.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>182</v>
       </c>
@@ -21574,7 +21584,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>185</v>
       </c>
@@ -21684,7 +21694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>188</v>
       </c>
@@ -21794,7 +21804,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>191</v>
       </c>
@@ -21904,7 +21914,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>194</v>
       </c>
@@ -22014,7 +22024,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>197</v>
       </c>
@@ -22124,7 +22134,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>200</v>
       </c>
@@ -22234,7 +22244,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>202</v>
       </c>
@@ -22344,7 +22354,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>205</v>
       </c>
@@ -22454,7 +22464,7 @@
         <v>0.14599999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>257</v>
       </c>
@@ -22564,7 +22574,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>115</v>
       </c>
@@ -22674,7 +22684,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>116</v>
       </c>
@@ -22784,7 +22794,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -22894,7 +22904,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>118</v>
       </c>
@@ -23004,7 +23014,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>119</v>
       </c>
@@ -23114,7 +23124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>270</v>
       </c>
@@ -23125,7 +23135,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>273</v>
       </c>
@@ -23235,7 +23245,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>276</v>
       </c>
@@ -23345,7 +23355,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>279</v>
       </c>
@@ -23455,7 +23465,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -23565,7 +23575,7 @@
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>285</v>
       </c>
@@ -23675,7 +23685,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>288</v>
       </c>
@@ -23785,7 +23795,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -23895,7 +23905,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>294</v>
       </c>
@@ -24005,7 +24015,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>120</v>
       </c>
@@ -24115,7 +24125,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>299</v>
       </c>
@@ -24225,7 +24235,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>302</v>
       </c>
@@ -24335,7 +24345,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>121</v>
       </c>
@@ -24456,12 +24466,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -24586,7 +24596,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -24711,7 +24721,7 @@
         <v>0.99959043283501392</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -24836,7 +24846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -24961,7 +24971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25086,7 +25096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -25211,7 +25221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -25336,7 +25346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25472,12 +25482,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>127</v>
       </c>
@@ -25602,7 +25612,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -25697,7 +25707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -25792,7 +25802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -25887,7 +25897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -25982,7 +25992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -26077,7 +26087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -26172,7 +26182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -26275,9 +26285,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AJ59"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -26375,27 +26385,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>147</v>
       </c>
@@ -26502,7 +26512,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>310</v>
       </c>
@@ -26510,7 +26520,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>153</v>
       </c>
@@ -26518,7 +26528,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>155</v>
       </c>
@@ -26628,7 +26638,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -26738,7 +26748,7 @@
         <v>-0.115</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>162</v>
       </c>
@@ -26848,7 +26858,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>165</v>
       </c>
@@ -26856,7 +26866,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>167</v>
       </c>
@@ -26966,7 +26976,7 @@
         <v>-3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>170</v>
       </c>
@@ -27076,7 +27086,7 @@
         <v>-3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>173</v>
       </c>
@@ -27186,7 +27196,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>176</v>
       </c>
@@ -27296,7 +27306,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>179</v>
       </c>
@@ -27406,7 +27416,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>182</v>
       </c>
@@ -27516,7 +27526,7 @@
         <v>-8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>185</v>
       </c>
@@ -27626,7 +27636,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>188</v>
       </c>
@@ -27736,7 +27746,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>191</v>
       </c>
@@ -27846,7 +27856,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>194</v>
       </c>
@@ -27956,7 +27966,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>197</v>
       </c>
@@ -28066,7 +28076,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>200</v>
       </c>
@@ -28176,7 +28186,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -28286,7 +28296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -28396,7 +28406,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>208</v>
       </c>
@@ -28506,7 +28516,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>24</v>
       </c>
@@ -28616,7 +28626,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>330</v>
       </c>
@@ -28624,7 +28634,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>218</v>
       </c>
@@ -28632,7 +28642,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -28742,7 +28752,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>159</v>
       </c>
@@ -28852,7 +28862,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>224</v>
       </c>
@@ -28962,7 +28972,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>227</v>
       </c>
@@ -28970,7 +28980,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -29080,7 +29090,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>170</v>
       </c>
@@ -29190,7 +29200,7 @@
         <v>-0.11600000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>173</v>
       </c>
@@ -29300,7 +29310,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>176</v>
       </c>
@@ -29410,7 +29420,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>179</v>
       </c>
@@ -29520,7 +29530,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>182</v>
       </c>
@@ -29630,7 +29640,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>185</v>
       </c>
@@ -29740,7 +29750,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -29850,7 +29860,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -29960,7 +29970,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>194</v>
       </c>
@@ -30070,7 +30080,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>197</v>
       </c>
@@ -30180,7 +30190,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>200</v>
       </c>
@@ -30290,7 +30300,7 @@
         <v>-2.7E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>202</v>
       </c>
@@ -30400,7 +30410,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>205</v>
       </c>
@@ -30510,7 +30520,7 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>257</v>
       </c>
@@ -30620,7 +30630,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -30730,7 +30740,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -30849,29 +30859,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E495E93-490C-4630-BB04-9B57B46A213E}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>919</v>
       </c>
@@ -30906,7 +30916,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2050</v>
       </c>
@@ -30941,7 +30951,7 @@
         <v>968.61480700000004</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2049</v>
       </c>
@@ -30976,7 +30986,7 @@
         <v>975.68035899999995</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2048</v>
       </c>
@@ -31011,7 +31021,7 @@
         <v>981.37280299999998</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2047</v>
       </c>
@@ -31046,7 +31056,7 @@
         <v>975.81964100000005</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2046</v>
       </c>
@@ -31081,7 +31091,7 @@
         <v>980.589966</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2045</v>
       </c>
@@ -31116,7 +31126,7 @@
         <v>984.091858</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2044</v>
       </c>
@@ -31151,7 +31161,7 @@
         <v>976.13824499999998</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2043</v>
       </c>
@@ -31186,7 +31196,7 @@
         <v>977.10333300000002</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2042</v>
       </c>
@@ -31221,7 +31231,7 @@
         <v>979.39685099999997</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2041</v>
       </c>
@@ -31256,7 +31266,7 @@
         <v>979.05828899999995</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2040</v>
       </c>
@@ -31291,7 +31301,7 @@
         <v>979.86975099999995</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2039</v>
       </c>
@@ -31326,7 +31336,7 @@
         <v>981.14685099999997</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2038</v>
       </c>
@@ -31361,7 +31371,7 @@
         <v>979.91186500000003</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2037</v>
       </c>
@@ -31396,7 +31406,7 @@
         <v>977.93768299999999</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2036</v>
       </c>
@@ -31431,7 +31441,7 @@
         <v>982.68225099999995</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2035</v>
       </c>
@@ -31466,7 +31476,7 @@
         <v>985.55090299999995</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2034</v>
       </c>
@@ -31501,7 +31511,7 @@
         <v>980.60241699999995</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2033</v>
       </c>
@@ -31536,7 +31546,7 @@
         <v>977.975098</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2032</v>
       </c>
@@ -31571,7 +31581,7 @@
         <v>975.89404300000001</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2031</v>
       </c>
@@ -31606,7 +31616,7 @@
         <v>972.47125200000005</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2030</v>
       </c>
@@ -31641,7 +31651,7 @@
         <v>970.98468000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2029</v>
       </c>
@@ -31676,7 +31686,7 @@
         <v>981.23956299999998</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2028</v>
       </c>
@@ -31711,7 +31721,7 @@
         <v>966.18756099999996</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2027</v>
       </c>
@@ -31746,7 +31756,7 @@
         <v>953.71936000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2026</v>
       </c>
@@ -31781,7 +31791,7 @@
         <v>966.38690199999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2025</v>
       </c>
@@ -31816,7 +31826,7 @@
         <v>964.77038600000003</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2024</v>
       </c>
@@ -31851,7 +31861,7 @@
         <v>940.58337400000005</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2023</v>
       </c>
@@ -31886,7 +31896,7 @@
         <v>906.911743</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2022</v>
       </c>
@@ -31921,7 +31931,7 @@
         <v>878.96453899999995</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -31956,7 +31966,7 @@
         <v>822.79125999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2020</v>
       </c>
@@ -31991,7 +32001,7 @@
         <v>728.74066200000004</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2019</v>
       </c>
@@ -32004,9 +32014,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ262"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1">
         <v>2020</v>
       </c>
@@ -32104,27 +32114,27 @@
         <v>150</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>147</v>
       </c>
@@ -32231,7 +32241,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
@@ -32239,7 +32249,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>400</v>
       </c>
@@ -32247,7 +32257,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>401</v>
       </c>
@@ -32255,7 +32265,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>402</v>
       </c>
@@ -32365,7 +32375,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>404</v>
       </c>
@@ -32475,7 +32485,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>406</v>
       </c>
@@ -32585,7 +32595,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>408</v>
       </c>
@@ -32695,7 +32705,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>410</v>
       </c>
@@ -32805,7 +32815,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>282</v>
       </c>
@@ -32915,7 +32925,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>413</v>
       </c>
@@ -33025,7 +33035,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>415</v>
       </c>
@@ -33135,7 +33145,7 @@
         <v>0.14399999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>294</v>
       </c>
@@ -33245,7 +33255,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>418</v>
       </c>
@@ -33355,7 +33365,7 @@
         <v>2.3E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>420</v>
       </c>
@@ -33363,7 +33373,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>402</v>
       </c>
@@ -33473,7 +33483,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>404</v>
       </c>
@@ -33583,7 +33593,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>406</v>
       </c>
@@ -33693,7 +33703,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>408</v>
       </c>
@@ -33803,7 +33813,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>410</v>
       </c>
@@ -33913,7 +33923,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>282</v>
       </c>
@@ -34023,7 +34033,7 @@
         <v>0.129</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>413</v>
       </c>
@@ -34133,7 +34143,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>415</v>
       </c>
@@ -34243,7 +34253,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>294</v>
       </c>
@@ -34353,7 +34363,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>430</v>
       </c>
@@ -34463,7 +34473,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>432</v>
       </c>
@@ -34471,7 +34481,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>402</v>
       </c>
@@ -34581,7 +34591,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>404</v>
       </c>
@@ -34691,7 +34701,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>406</v>
       </c>
@@ -34801,7 +34811,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>408</v>
       </c>
@@ -34911,7 +34921,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>410</v>
       </c>
@@ -35021,7 +35031,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>282</v>
       </c>
@@ -35131,7 +35141,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>413</v>
       </c>
@@ -35241,7 +35251,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>415</v>
       </c>
@@ -35351,7 +35361,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>294</v>
       </c>
@@ -35461,7 +35471,7 @@
         <v>0.11899999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>442</v>
       </c>
@@ -35571,7 +35581,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>444</v>
       </c>
@@ -35681,7 +35691,7 @@
         <v>1.6E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>446</v>
       </c>
@@ -35689,7 +35699,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>401</v>
       </c>
@@ -35697,7 +35707,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>402</v>
       </c>
@@ -35807,7 +35817,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>404</v>
       </c>
@@ -35917,7 +35927,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>406</v>
       </c>
@@ -36027,7 +36037,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>408</v>
       </c>
@@ -36137,7 +36147,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>410</v>
       </c>
@@ -36247,7 +36257,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>282</v>
       </c>
@@ -36357,7 +36367,7 @@
         <v>0.13200000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>413</v>
       </c>
@@ -36467,7 +36477,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>415</v>
       </c>
@@ -36577,7 +36587,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>294</v>
       </c>
@@ -36687,7 +36697,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>418</v>
       </c>
@@ -36797,7 +36807,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>420</v>
       </c>
@@ -36805,7 +36815,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>402</v>
       </c>
@@ -36915,7 +36925,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>404</v>
       </c>
@@ -37025,7 +37035,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>406</v>
       </c>
@@ -37135,7 +37145,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>408</v>
       </c>
@@ -37245,7 +37255,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>410</v>
       </c>
@@ -37355,7 +37365,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>282</v>
       </c>
@@ -37465,7 +37475,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>413</v>
       </c>
@@ -37575,7 +37585,7 @@
         <v>0.13500000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>415</v>
       </c>
@@ -37685,7 +37695,7 @@
         <v>0.13600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>294</v>
       </c>
@@ -37795,7 +37805,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>430</v>
       </c>
@@ -37905,7 +37915,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>432</v>
       </c>
@@ -37913,7 +37923,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>402</v>
       </c>
@@ -38023,7 +38033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>404</v>
       </c>
@@ -38133,7 +38143,7 @@
         <v>-2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>406</v>
       </c>
@@ -38243,7 +38253,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>408</v>
       </c>
@@ -38353,7 +38363,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>410</v>
       </c>
@@ -38463,7 +38473,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>282</v>
       </c>
@@ -38573,7 +38583,7 @@
         <v>0.113</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>413</v>
       </c>
@@ -38683,7 +38693,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>415</v>
       </c>
@@ -38793,7 +38803,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>294</v>
       </c>
@@ -38903,7 +38913,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>442</v>
       </c>
@@ -39013,7 +39023,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>401</v>
       </c>
@@ -39024,7 +39034,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="87" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>402</v>
       </c>
@@ -39134,7 +39144,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="88" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>404</v>
       </c>
@@ -39244,7 +39254,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>406</v>
       </c>
@@ -39354,7 +39364,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>408</v>
       </c>
@@ -39464,7 +39474,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>410</v>
       </c>
@@ -39574,7 +39584,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>282</v>
       </c>
@@ -39684,7 +39694,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>413</v>
       </c>
@@ -39794,7 +39804,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>415</v>
       </c>
@@ -39904,7 +39914,7 @@
         <v>0.114</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>294</v>
       </c>
@@ -40014,7 +40024,7 @@
         <v>0.13400000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>487</v>
       </c>
@@ -40124,7 +40134,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>489</v>
       </c>
@@ -40132,7 +40142,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>401</v>
       </c>
@@ -40140,7 +40150,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="99" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>402</v>
       </c>
@@ -40250,7 +40260,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>404</v>
       </c>
@@ -40360,7 +40370,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>406</v>
       </c>
@@ -40470,7 +40480,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="102" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>408</v>
       </c>
@@ -40580,7 +40590,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="103" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>410</v>
       </c>
@@ -40690,7 +40700,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="104" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>282</v>
       </c>
@@ -40800,7 +40810,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>413</v>
       </c>
@@ -40910,7 +40920,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="106" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>415</v>
       </c>
@@ -41020,7 +41030,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>294</v>
       </c>
@@ -41130,7 +41140,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="108" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>499</v>
       </c>
@@ -41237,7 +41247,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="109" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>420</v>
       </c>
@@ -41245,7 +41255,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="110" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>402</v>
       </c>
@@ -41355,7 +41365,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>404</v>
       </c>
@@ -41465,7 +41475,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="112" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>406</v>
       </c>
@@ -41575,7 +41585,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="113" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>408</v>
       </c>
@@ -41685,7 +41695,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>410</v>
       </c>
@@ -41795,7 +41805,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>282</v>
       </c>
@@ -41905,7 +41915,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="116" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>413</v>
       </c>
@@ -42015,7 +42025,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="117" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>415</v>
       </c>
@@ -42125,7 +42135,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="118" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>294</v>
       </c>
@@ -42235,7 +42245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>510</v>
       </c>
@@ -42342,7 +42352,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>432</v>
       </c>
@@ -42350,7 +42360,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="121" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>402</v>
       </c>
@@ -42460,7 +42470,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="122" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>404</v>
       </c>
@@ -42570,7 +42580,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="123" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>406</v>
       </c>
@@ -42680,7 +42690,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="124" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>408</v>
       </c>
@@ -42790,7 +42800,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="125" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>410</v>
       </c>
@@ -42900,7 +42910,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>282</v>
       </c>
@@ -43010,7 +43020,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>413</v>
       </c>
@@ -43120,7 +43130,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="128" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>415</v>
       </c>
@@ -43230,7 +43240,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="129" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>294</v>
       </c>
@@ -43340,7 +43350,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="130" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>521</v>
       </c>
@@ -43447,7 +43457,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="131" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>523</v>
       </c>
@@ -43554,7 +43564,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>525</v>
       </c>
@@ -43562,7 +43572,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="133" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>401</v>
       </c>
@@ -43570,7 +43580,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="134" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>402</v>
       </c>
@@ -43680,7 +43690,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>404</v>
       </c>
@@ -43790,7 +43800,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>406</v>
       </c>
@@ -43900,7 +43910,7 @@
         <v>0.11600000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>408</v>
       </c>
@@ -44010,7 +44020,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>410</v>
       </c>
@@ -44120,7 +44130,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>282</v>
       </c>
@@ -44230,7 +44240,7 @@
         <v>0.14299999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>413</v>
       </c>
@@ -44340,7 +44350,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="141" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>415</v>
       </c>
@@ -44450,7 +44460,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="142" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>294</v>
       </c>
@@ -44560,7 +44570,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="143" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>418</v>
       </c>
@@ -44670,7 +44680,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>420</v>
       </c>
@@ -44678,7 +44688,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="145" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>402</v>
       </c>
@@ -44788,7 +44798,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>404</v>
       </c>
@@ -44898,7 +44908,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>406</v>
       </c>
@@ -45008,7 +45018,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>408</v>
       </c>
@@ -45118,7 +45128,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>410</v>
       </c>
@@ -45228,7 +45238,7 @@
         <v>7.3999999999999996E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>282</v>
       </c>
@@ -45338,7 +45348,7 @@
         <v>0.13900000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>413</v>
       </c>
@@ -45448,7 +45458,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="152" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>415</v>
       </c>
@@ -45558,7 +45568,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="153" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>294</v>
       </c>
@@ -45668,7 +45678,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="154" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>430</v>
       </c>
@@ -45778,7 +45788,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>432</v>
       </c>
@@ -45786,7 +45796,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="156" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>402</v>
       </c>
@@ -45896,7 +45906,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="157" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>404</v>
       </c>
@@ -46006,7 +46016,7 @@
         <v>-4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>406</v>
       </c>
@@ -46116,7 +46126,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="159" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>408</v>
       </c>
@@ -46226,7 +46236,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>410</v>
       </c>
@@ -46336,7 +46346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>282</v>
       </c>
@@ -46446,7 +46456,7 @@
         <v>0.13700000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>413</v>
       </c>
@@ -46556,7 +46566,7 @@
         <v>0.124</v>
       </c>
     </row>
-    <row r="163" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>415</v>
       </c>
@@ -46666,7 +46676,7 @@
         <v>0.123</v>
       </c>
     </row>
-    <row r="164" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>294</v>
       </c>
@@ -46776,7 +46786,7 @@
         <v>0.126</v>
       </c>
     </row>
-    <row r="165" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>442</v>
       </c>
@@ -46886,7 +46896,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>21</v>
       </c>
@@ -46996,7 +47006,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -47004,7 +47014,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="168" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>489</v>
       </c>
@@ -47012,7 +47022,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="169" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>401</v>
       </c>
@@ -47020,7 +47030,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="170" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>402</v>
       </c>
@@ -47130,7 +47140,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>404</v>
       </c>
@@ -47240,7 +47250,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>406</v>
       </c>
@@ -47350,7 +47360,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>408</v>
       </c>
@@ -47460,7 +47470,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>410</v>
       </c>
@@ -47570,7 +47580,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>282</v>
       </c>
@@ -47680,7 +47690,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>413</v>
       </c>
@@ -47790,7 +47800,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>415</v>
       </c>
@@ -47900,7 +47910,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>294</v>
       </c>
@@ -48010,7 +48020,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>499</v>
       </c>
@@ -48117,7 +48127,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>420</v>
       </c>
@@ -48125,7 +48135,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="181" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>402</v>
       </c>
@@ -48235,7 +48245,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="182" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>404</v>
       </c>
@@ -48345,7 +48355,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>406</v>
       </c>
@@ -48455,7 +48465,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="184" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>408</v>
       </c>
@@ -48565,7 +48575,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="185" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>410</v>
       </c>
@@ -48675,7 +48685,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>282</v>
       </c>
@@ -48785,7 +48795,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>413</v>
       </c>
@@ -48895,7 +48905,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>415</v>
       </c>
@@ -49005,7 +49015,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>294</v>
       </c>
@@ -49115,7 +49125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>510</v>
       </c>
@@ -49222,7 +49232,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>432</v>
       </c>
@@ -49230,7 +49240,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="192" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>402</v>
       </c>
@@ -49340,7 +49350,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>404</v>
       </c>
@@ -49450,7 +49460,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>406</v>
       </c>
@@ -49560,7 +49570,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>408</v>
       </c>
@@ -49670,7 +49680,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>410</v>
       </c>
@@ -49780,7 +49790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>282</v>
       </c>
@@ -49890,7 +49900,7 @@
         <v>1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>413</v>
       </c>
@@ -50000,7 +50010,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="199" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>415</v>
       </c>
@@ -50110,7 +50120,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>294</v>
       </c>
@@ -50220,7 +50230,7 @@
         <v>3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>521</v>
       </c>
@@ -50327,7 +50337,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>523</v>
       </c>
@@ -50434,7 +50444,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>588</v>
       </c>
@@ -50442,7 +50452,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="204" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>401</v>
       </c>
@@ -50450,7 +50460,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="205" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>402</v>
       </c>
@@ -50560,7 +50570,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>404</v>
       </c>
@@ -50670,7 +50680,7 @@
         <v>2.7E-2</v>
       </c>
     </row>
-    <row r="207" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>406</v>
       </c>
@@ -50780,7 +50790,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>408</v>
       </c>
@@ -50890,7 +50900,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="209" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>410</v>
       </c>
@@ -51000,7 +51010,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>282</v>
       </c>
@@ -51110,7 +51120,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>413</v>
       </c>
@@ -51220,7 +51230,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>415</v>
       </c>
@@ -51330,7 +51340,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>294</v>
       </c>
@@ -51440,7 +51450,7 @@
         <v>-4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>418</v>
       </c>
@@ -51550,7 +51560,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>420</v>
       </c>
@@ -51558,7 +51568,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="216" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>402</v>
       </c>
@@ -51668,7 +51678,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>404</v>
       </c>
@@ -51778,7 +51788,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>406</v>
       </c>
@@ -51888,7 +51898,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="219" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>408</v>
       </c>
@@ -51998,7 +52008,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="220" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>410</v>
       </c>
@@ -52108,7 +52118,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>282</v>
       </c>
@@ -52218,7 +52228,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="222" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>413</v>
       </c>
@@ -52328,7 +52338,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="223" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>415</v>
       </c>
@@ -52438,7 +52448,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="224" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>294</v>
       </c>
@@ -52548,7 +52558,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="225" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>430</v>
       </c>
@@ -52658,7 +52668,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>432</v>
       </c>
@@ -52666,7 +52676,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="227" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>402</v>
       </c>
@@ -52776,7 +52786,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>404</v>
       </c>
@@ -52886,7 +52896,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="229" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>406</v>
       </c>
@@ -52996,7 +53006,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="230" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>408</v>
       </c>
@@ -53106,7 +53116,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>410</v>
       </c>
@@ -53216,7 +53226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>282</v>
       </c>
@@ -53326,7 +53336,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>413</v>
       </c>
@@ -53436,7 +53446,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>415</v>
       </c>
@@ -53546,7 +53556,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>294</v>
       </c>
@@ -53656,7 +53666,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>442</v>
       </c>
@@ -53766,7 +53776,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="237" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>270</v>
       </c>
@@ -53876,7 +53886,7 @@
         <v>1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -53884,7 +53894,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="239" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>620</v>
       </c>
@@ -53994,7 +54004,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="240" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>622</v>
       </c>
@@ -54104,7 +54114,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>624</v>
       </c>
@@ -54112,7 +54122,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="242" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>625</v>
       </c>
@@ -54222,7 +54232,7 @@
         <v>-1.7000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>627</v>
       </c>
@@ -54332,7 +54342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>629</v>
       </c>
@@ -54442,7 +54452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="245" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>631</v>
       </c>
@@ -54552,7 +54562,7 @@
         <v>0.223</v>
       </c>
     </row>
-    <row r="246" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>38</v>
       </c>
@@ -54560,7 +54570,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="247" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>633</v>
       </c>
@@ -54670,7 +54680,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>622</v>
       </c>
@@ -54780,7 +54790,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="249" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>624</v>
       </c>
@@ -54788,7 +54798,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="250" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>625</v>
       </c>
@@ -54898,7 +54908,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>627</v>
       </c>
@@ -55008,7 +55018,7 @@
         <v>-6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>629</v>
       </c>
@@ -55118,7 +55128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>631</v>
       </c>
@@ -55228,7 +55238,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>37</v>
       </c>
@@ -55236,7 +55246,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="255" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>640</v>
       </c>
@@ -55346,7 +55356,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="256" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>642</v>
       </c>
@@ -55456,7 +55466,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>644</v>
       </c>
@@ -55566,7 +55576,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>624</v>
       </c>
@@ -55574,7 +55584,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="259" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>625</v>
       </c>
@@ -55684,7 +55694,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="260" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>627</v>
       </c>
@@ -55794,7 +55804,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>629</v>
       </c>
@@ -55904,7 +55914,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="262" spans="1:36" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>631</v>
       </c>
@@ -56023,18 +56033,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
-    <col min="6" max="8" width="23.26953125" customWidth="1"/>
-    <col min="10" max="10" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>128</v>
       </c>
@@ -56060,7 +56070,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -56087,7 +56097,7 @@
       </c>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -56095,7 +56105,7 @@
         <v>300</v>
       </c>
       <c r="C3" s="5">
-        <v>127466.0117345309</v>
+        <v>142618.8307345309</v>
       </c>
       <c r="D3" s="5">
         <v>100403.17008274974</v>
@@ -56115,7 +56125,7 @@
       <c r="I3" s="5"/>
       <c r="J3" s="24"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -56129,7 +56139,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="5">
-        <v>2120.6909179999998</v>
+        <v>5561.7944340000004</v>
       </c>
       <c r="F4" s="5">
         <v>0</v>
@@ -56141,12 +56151,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="5">
-        <v>1897.4974391190394</v>
+        <v>2563.6060360683009</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -56155,7 +56165,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="5">
-        <v>625.20256088096039</v>
+        <v>173.39396393169866</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -56167,7 +56177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -56193,7 +56203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -56219,7 +56229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -56236,19 +56246,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.81640625" customWidth="1"/>
-    <col min="4" max="4" width="18.26953125" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" customWidth="1"/>
-    <col min="6" max="8" width="23.26953125" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="8" width="23.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>128</v>
       </c>
@@ -56274,7 +56284,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -56302,7 +56312,7 @@
       <c r="I2" s="24"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -56329,7 +56339,7 @@
       </c>
       <c r="J3" s="5"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -56355,7 +56365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -56381,7 +56391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -56395,7 +56405,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>10518</v>
+        <v>10524</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -56407,7 +56417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -56441,81 +56451,81 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AE136"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="58.26953125" customWidth="1"/>
+    <col min="1" max="1" width="58.28515625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>64</v>
       </c>
       <c r="N15" s="33"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>89</v>
       </c>
       <c r="N16" s="35"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>90</v>
       </c>
@@ -56524,13 +56534,13 @@
       <c r="P17" s="36"/>
       <c r="Q17" s="36"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N18" s="36"/>
       <c r="O18" s="37"/>
       <c r="P18" s="37"/>
       <c r="Q18" s="37"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -56539,7 +56549,7 @@
       <c r="P19" s="37"/>
       <c r="Q19" s="37"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -56548,7 +56558,7 @@
       <c r="P20" s="37"/>
       <c r="Q20" s="37"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>93</v>
       </c>
@@ -56557,7 +56567,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>94</v>
       </c>
@@ -56566,7 +56576,7 @@
       <c r="P22" s="37"/>
       <c r="Q22" s="37"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>95</v>
       </c>
@@ -56575,7 +56585,7 @@
       <c r="P23" s="37"/>
       <c r="Q23" s="37"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>96</v>
       </c>
@@ -56584,7 +56594,7 @@
       <c r="P24" s="37"/>
       <c r="Q24" s="37"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -56593,13 +56603,13 @@
       <c r="P25" s="37"/>
       <c r="Q25" s="37"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N26" s="36"/>
       <c r="O26" s="38"/>
       <c r="P26" s="37"/>
       <c r="Q26" s="37"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>930</v>
       </c>
@@ -56608,13 +56618,13 @@
       <c r="P27" s="37"/>
       <c r="Q27" s="37"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N28" s="36"/>
       <c r="O28" s="38"/>
       <c r="P28" s="37"/>
       <c r="Q28" s="37"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>945</v>
       </c>
@@ -56623,13 +56633,13 @@
       <c r="P29" s="37"/>
       <c r="Q29" s="37"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="N30" s="36"/>
       <c r="O30" s="38"/>
       <c r="P30" s="37"/>
       <c r="Q30" s="37"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
         <v>946</v>
       </c>
@@ -56638,7 +56648,7 @@
       <c r="P31" s="37"/>
       <c r="Q31" s="37"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="28"/>
       <c r="B32" t="s">
         <v>947</v>
@@ -56657,7 +56667,7 @@
       <c r="P32" s="37"/>
       <c r="Q32" s="37"/>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="42">
         <v>44947</v>
       </c>
@@ -56678,7 +56688,7 @@
       <c r="P33" s="37"/>
       <c r="Q33" s="37"/>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="42">
         <v>44978</v>
       </c>
@@ -56699,7 +56709,7 @@
       <c r="P34" s="37"/>
       <c r="Q34" s="37"/>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="42">
         <v>45006</v>
       </c>
@@ -56720,7 +56730,7 @@
       <c r="P35" s="37"/>
       <c r="Q35" s="37"/>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="42">
         <v>45037</v>
       </c>
@@ -56741,7 +56751,7 @@
       <c r="P36" s="37"/>
       <c r="Q36" s="37"/>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="42">
         <v>45067</v>
       </c>
@@ -56762,7 +56772,7 @@
       <c r="P37" s="37"/>
       <c r="Q37" s="37"/>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="42">
         <v>45098</v>
       </c>
@@ -56783,7 +56793,7 @@
       <c r="P38" s="37"/>
       <c r="Q38" s="37"/>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="42">
         <v>45128</v>
       </c>
@@ -56816,7 +56826,7 @@
       <c r="AC39" s="11"/>
       <c r="AD39" s="11"/>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="42">
         <v>45159</v>
       </c>
@@ -56837,7 +56847,7 @@
       <c r="P40" s="37"/>
       <c r="Q40" s="37"/>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="42">
         <v>45190</v>
       </c>
@@ -56858,7 +56868,7 @@
       <c r="P41" s="37"/>
       <c r="Q41" s="37"/>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="42">
         <v>45220</v>
       </c>
@@ -56879,7 +56889,7 @@
       <c r="P42" s="37"/>
       <c r="Q42" s="37"/>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="42">
         <v>45251</v>
       </c>
@@ -56900,7 +56910,7 @@
       <c r="P43" s="37"/>
       <c r="Q43" s="37"/>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="42">
         <v>45281</v>
       </c>
@@ -56921,7 +56931,7 @@
       <c r="P44" s="37"/>
       <c r="Q44" s="37"/>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="42">
         <v>44948</v>
       </c>
@@ -56942,7 +56952,7 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="42">
         <v>44979</v>
       </c>
@@ -56963,7 +56973,7 @@
       <c r="P46" s="37"/>
       <c r="Q46" s="37"/>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="42">
         <v>45007</v>
       </c>
@@ -56984,7 +56994,7 @@
       <c r="P47" s="37"/>
       <c r="Q47" s="37"/>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="42">
         <v>45038</v>
       </c>
@@ -57005,7 +57015,7 @@
       <c r="P48" s="37"/>
       <c r="Q48" s="37"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A49" s="42">
         <v>45068</v>
       </c>
@@ -57026,7 +57036,7 @@
       <c r="P49" s="37"/>
       <c r="Q49" s="37"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A50" s="42">
         <v>45099</v>
       </c>
@@ -57047,7 +57057,7 @@
       <c r="P50" s="37"/>
       <c r="Q50" s="37"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A51" s="42">
         <v>45129</v>
       </c>
@@ -57068,7 +57078,7 @@
       <c r="P51" s="37"/>
       <c r="Q51" s="37"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A52" s="42">
         <v>45160</v>
       </c>
@@ -57089,7 +57099,7 @@
       <c r="P52" s="37"/>
       <c r="Q52" s="37"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A53" s="42">
         <v>45191</v>
       </c>
@@ -57110,7 +57120,7 @@
       <c r="P53" s="37"/>
       <c r="Q53" s="37"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A54" s="42">
         <v>45221</v>
       </c>
@@ -57131,7 +57141,7 @@
       <c r="P54" s="37"/>
       <c r="Q54" s="37"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A55" s="42">
         <v>45252</v>
       </c>
@@ -57152,7 +57162,7 @@
       <c r="P55" s="37"/>
       <c r="Q55" s="37"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A56" s="42">
         <v>45282</v>
       </c>
@@ -57173,13 +57183,13 @@
       <c r="P56" s="37"/>
       <c r="Q56" s="37"/>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
       <c r="N57" s="36"/>
       <c r="O57" s="38"/>
       <c r="P57" s="37"/>
       <c r="Q57" s="37"/>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>951</v>
       </c>
@@ -57196,7 +57206,7 @@
       <c r="P58" s="37"/>
       <c r="Q58" s="37"/>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>952</v>
       </c>
@@ -57213,7 +57223,7 @@
       <c r="P59" s="37"/>
       <c r="Q59" s="37"/>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>931</v>
       </c>
@@ -57308,7 +57318,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>953</v>
       </c>
@@ -57403,7 +57413,7 @@
         <v>15079600</v>
       </c>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>954</v>
       </c>
@@ -57498,7 +57508,7 @@
         <v>6006</v>
       </c>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>955</v>
       </c>
@@ -57593,7 +57603,7 @@
         <v>6490060</v>
       </c>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>956</v>
       </c>
@@ -57688,7 +57698,7 @@
         <v>185550</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>957</v>
       </c>
@@ -57783,7 +57793,7 @@
         <v>507957</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>958</v>
       </c>
@@ -57878,7 +57888,7 @@
         <v>5433</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>959</v>
       </c>
@@ -57973,7 +57983,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>931</v>
       </c>
@@ -58068,7 +58078,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>960</v>
       </c>
@@ -58163,7 +58173,7 @@
         <v>12739700</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>961</v>
       </c>
@@ -58258,7 +58268,7 @@
         <v>8181.79</v>
       </c>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>962</v>
       </c>
@@ -58353,7 +58363,7 @@
         <v>8837860</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>963</v>
       </c>
@@ -58448,7 +58458,7 @@
         <v>252673</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>964</v>
       </c>
@@ -58543,7 +58553,7 @@
         <v>429138</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>965</v>
       </c>
@@ -58638,7 +58648,7 @@
         <v>7398.52</v>
       </c>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>966</v>
       </c>
@@ -58733,7 +58743,7 @@
         <v>1864.12</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>932</v>
       </c>
@@ -58858,7 +58868,7 @@
         <v>0.67691915148896309</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>933</v>
       </c>
@@ -58983,7 +58993,7 @@
         <v>2.2802051873582804E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>934</v>
       </c>
@@ -59108,7 +59118,7 @@
         <v>0.69972120336254584</v>
       </c>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>932</v>
       </c>
@@ -59233,7 +59243,7 @@
         <v>0.571881561798261</v>
       </c>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>933</v>
       </c>
@@ -59358,7 +59368,7 @@
         <v>1.9263884523731498E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>934</v>
       </c>
@@ -59483,7 +59493,7 @@
         <v>0.59114544632199251</v>
       </c>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B86" s="40"/>
       <c r="C86" s="40"/>
       <c r="D86" s="40"/>
@@ -59515,7 +59525,7 @@
       <c r="AD86" s="40"/>
       <c r="AE86" s="40"/>
     </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>967</v>
       </c>
@@ -59523,7 +59533,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
         <v>976</v>
       </c>
@@ -59531,7 +59541,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2021</v>
       </c>
@@ -59543,7 +59553,7 @@
         <v>1.0567375886524823E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2022</v>
       </c>
@@ -59555,7 +59565,7 @@
         <v>1.6308663341138147E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>931</v>
       </c>
@@ -59650,7 +59660,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>969</v>
       </c>
@@ -59745,7 +59755,7 @@
         <v>97356</v>
       </c>
     </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>970</v>
       </c>
@@ -59840,7 +59850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>971</v>
       </c>
@@ -59935,7 +59945,7 @@
         <v>16023</v>
       </c>
     </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>972</v>
       </c>
@@ -60030,7 +60040,7 @@
         <v>52962</v>
       </c>
     </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>973</v>
       </c>
@@ -60125,7 +60135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>974</v>
       </c>
@@ -60220,7 +60230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>975</v>
       </c>
@@ -60315,7 +60325,7 @@
         <v>8232</v>
       </c>
     </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>978</v>
       </c>
@@ -60440,7 +60450,7 @@
         <v>0.55742210312961626</v>
       </c>
     </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>979</v>
       </c>
@@ -60565,7 +60575,7 @@
         <v>4.7133189048060735E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>999</v>
       </c>
@@ -60690,12 +60700,12 @@
         <v>0.60455529217767701</v>
       </c>
     </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>931</v>
       </c>
@@ -60790,7 +60800,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>981</v>
       </c>
@@ -60885,7 +60895,7 @@
         <v>1107250</v>
       </c>
     </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>982</v>
       </c>
@@ -60980,7 +60990,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>983</v>
       </c>
@@ -61075,7 +61085,7 @@
         <v>922863</v>
       </c>
     </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>984</v>
       </c>
@@ -61170,7 +61180,7 @@
         <v>457686</v>
       </c>
     </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>985</v>
       </c>
@@ -61265,7 +61275,7 @@
         <v>34482</v>
       </c>
     </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>986</v>
       </c>
@@ -61360,7 +61370,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>987</v>
       </c>
@@ -61455,7 +61465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>978</v>
       </c>
@@ -61580,7 +61590,7 @@
         <v>0.43878976848068768</v>
       </c>
     </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>988</v>
       </c>
@@ -61705,7 +61715,7 @@
         <v>1.3664799093927364E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>979</v>
       </c>
@@ -61830,7 +61840,7 @@
         <v>7.1331820570353384E-6</v>
       </c>
     </row>
-    <row r="120" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>989</v>
       </c>
@@ -61955,12 +61965,12 @@
         <v>0.45246170075667208</v>
       </c>
     </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
         <v>931</v>
       </c>
@@ -62055,7 +62065,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>991</v>
       </c>
@@ -62150,7 +62160,7 @@
         <v>141528</v>
       </c>
     </row>
-    <row r="126" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>992</v>
       </c>
@@ -62245,7 +62255,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="127" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>993</v>
       </c>
@@ -62340,7 +62350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>994</v>
       </c>
@@ -62435,7 +62445,7 @@
         <v>130056</v>
       </c>
     </row>
-    <row r="129" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>995</v>
       </c>
@@ -62530,7 +62540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>996</v>
       </c>
@@ -62625,7 +62635,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="131" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>997</v>
       </c>
@@ -62720,7 +62730,7 @@
         <v>45099</v>
       </c>
     </row>
-    <row r="133" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>978</v>
       </c>
@@ -62845,7 +62855,7 @@
         <v>0.44366283279884888</v>
       </c>
     </row>
-    <row r="134" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>988</v>
       </c>
@@ -62970,7 +62980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>979</v>
       </c>
@@ -63095,7 +63105,7 @@
         <v>0.14137661873548193</v>
       </c>
     </row>
-    <row r="136" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>989</v>
       </c>
@@ -63236,19 +63246,19 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL93"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="18" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="9" width="9.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -63269,7 +63279,7 @@
       </c>
       <c r="R1" s="17"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -63292,7 +63302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -63315,7 +63325,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -63338,12 +63348,12 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -63358,7 +63368,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" s="12"/>
       <c r="B7" s="12"/>
       <c r="C7" s="12" t="s">
@@ -63373,7 +63383,7 @@
       </c>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:38" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="12"/>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
@@ -63384,7 +63394,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>9</v>
       </c>
@@ -63524,7 +63534,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -63668,7 +63678,7 @@
         <v>0.99913267926293059</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>2</v>
       </c>
@@ -63805,7 +63815,7 @@
         <v>1.2225974073810479E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>3</v>
       </c>
@@ -63940,7 +63950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>4</v>
       </c>
@@ -64077,7 +64087,7 @@
         <v>3.0818463927506201E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>5</v>
       </c>
@@ -64215,7 +64225,7 @@
         <v>4.9982798179070587E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>124</v>
       </c>
@@ -64352,7 +64362,7 @@
         <v>8.6165104068937348E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="23"/>
       <c r="B16" s="23"/>
       <c r="C16" s="23" t="s">
@@ -64492,7 +64502,7 @@
         <v>3.1062760226311276E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -64634,7 +64644,7 @@
         <v>0.99967234626801127</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>2</v>
       </c>
@@ -64770,7 +64780,7 @@
         <v>1.2353695258898144E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>3</v>
       </c>
@@ -64905,7 +64915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>4</v>
       </c>
@@ -65040,7 +65050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>5</v>
       </c>
@@ -65177,7 +65187,7 @@
         <v>4.9265458207603127E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>124</v>
       </c>
@@ -65314,7 +65324,7 @@
         <v>8.6165104068937001E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="23"/>
       <c r="B23" s="23"/>
       <c r="C23" s="23" t="s">
@@ -65454,7 +65464,7 @@
         <v>3.1058892203350341E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -65598,13 +65608,13 @@
         <v>0.9996355795222398</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>2</v>
       </c>
       <c r="E25" s="22">
         <f>'SYVbT-passenger'!D3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="F25" s="22">
         <f>F32*3</f>
@@ -65616,136 +65626,136 @@
       </c>
       <c r="I25" s="22">
         <f t="shared" si="1"/>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="J25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,J$9))</f>
-        <v>0.30043157833481504</v>
+        <v>0.29596244960239987</v>
       </c>
       <c r="K25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,K$9))</f>
-        <v>0.2997017384509349</v>
+        <v>0.29525559107671612</v>
       </c>
       <c r="L25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,L$9))</f>
-        <v>0.29872838007535607</v>
+        <v>0.29431288202296346</v>
       </c>
       <c r="M25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,M$9))</f>
-        <v>0.29743557082505373</v>
+        <v>0.2930607810336332</v>
       </c>
       <c r="N25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,N$9))</f>
-        <v>0.29572780273850224</v>
+        <v>0.29140678752282123</v>
       </c>
       <c r="O25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,O$9))</f>
-        <v>0.29348805553810225</v>
+        <v>0.28923756597307232</v>
       </c>
       <c r="P25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,P$9))</f>
-        <v>0.29057816867446151</v>
+        <v>0.28641930626464923</v>
       </c>
       <c r="Q25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Q$9))</f>
-        <v>0.28684357792599674</v>
+        <v>0.28280231112804816</v>
       </c>
       <c r="R25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,R$9))</f>
-        <v>0.28212505041848135</v>
+        <v>0.27823236164867954</v>
       </c>
       <c r="S25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,S$9))</f>
-        <v>0.27627995437001424</v>
+        <v>0.2725713172654462</v>
       </c>
       <c r="T25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,T$9))</f>
-        <v>0.26921392877955547</v>
+        <v>0.26572778823718668</v>
       </c>
       <c r="U25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,U$9))</f>
-        <v>0.26091971966867544</v>
+        <v>0.25769474900033379</v>
       </c>
       <c r="V25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,V$9))</f>
-        <v>0.25151367915559786</v>
+        <v>0.24858488795211589</v>
       </c>
       <c r="W25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,W$9))</f>
-        <v>0.24125472684112267</v>
+        <v>0.23864897177620478</v>
       </c>
       <c r="X25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,X$9))</f>
-        <v>0.23053064887219032</v>
+        <v>0.22826257592436899</v>
       </c>
       <c r="Y25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Y$9))</f>
-        <v>0.219806570903258</v>
+        <v>0.21787618007253318</v>
       </c>
       <c r="Z25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,Z$9))</f>
-        <v>0.20954761858878282</v>
+        <v>0.20794026389662207</v>
       </c>
       <c r="AA25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AA$9))</f>
-        <v>0.20014157807570523</v>
+        <v>0.19883040284840414</v>
       </c>
       <c r="AB25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AB$9))</f>
-        <v>0.19184736896482521</v>
+        <v>0.19079736361155128</v>
       </c>
       <c r="AC25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AC$9))</f>
-        <v>0.18478134337436644</v>
+        <v>0.18395383458329176</v>
       </c>
       <c r="AD25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AD$9))</f>
-        <v>0.1789362473258993</v>
+        <v>0.17829279020005839</v>
       </c>
       <c r="AE25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AE$9))</f>
-        <v>0.17421771981838394</v>
+        <v>0.17372284072068978</v>
       </c>
       <c r="AF25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AF$9))</f>
-        <v>0.17048312906991916</v>
+        <v>0.17010584558408873</v>
       </c>
       <c r="AG25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AG$9))</f>
-        <v>0.16757324220627842</v>
+        <v>0.16728758587566564</v>
       </c>
       <c r="AH25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AH$9))</f>
-        <v>0.16533349500587841</v>
+        <v>0.1651183643259167</v>
       </c>
       <c r="AI25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AI$9))</f>
-        <v>0.16362572691932695</v>
+        <v>0.16346437081510473</v>
       </c>
       <c r="AJ25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AJ$9))</f>
-        <v>0.16233291766902463</v>
+        <v>0.1622122698257745</v>
       </c>
       <c r="AK25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AK$9))</f>
-        <v>0.16135955929344575</v>
+        <v>0.16126956077202181</v>
       </c>
       <c r="AL25">
         <f>IF($G25="s-curve",$E25+($F25-$E25)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E25:$F25,$E$9:$F$9,AL$9))</f>
-        <v>0.16062971940956564</v>
-      </c>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
+        <v>0.16056270224633809</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>3</v>
       </c>
       <c r="E26" s="22">
         <f>'SYVbT-passenger'!D3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="F26" s="22">
         <f>E26</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="G26" s="7" t="str">
         <f>IF(E26=F26,"n/a",IF(OR(C26="battery electric vehicle",C26="natural gas vehicle",C26="plugin hybrid vehicle"),"s-curve","linear"))</f>
@@ -65753,126 +65763,126 @@
       </c>
       <c r="I26" s="22">
         <f t="shared" si="1"/>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="J26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,J$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="K26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,K$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="L26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,L$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="M26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,M$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="N26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,N$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="O26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,O$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="P26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,P$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Q26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Q$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="R26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,R$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="S26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,S$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="T26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,T$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="U26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,U$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="V26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,V$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="W26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,W$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="X26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,X$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Y26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Y$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="Z26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,Z$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AA26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AA$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AB26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AB$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AC26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AC$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AD26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AD$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AE26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AE$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AF26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AF$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AG26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AG$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AH26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AH$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AI26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AI$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AJ26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AJ$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AK26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AK$9))</f>
-        <v>0.30255990331064825</v>
+        <v>0.29802375741500553</v>
       </c>
       <c r="AL26">
         <f>IF($G26="s-curve",$E26+($F26-$E26)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E26:$F26,$E$9:$F$9,AL$9))</f>
-        <v>0.30255990331064825</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
+        <v>0.29802375741500553</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>4</v>
       </c>
@@ -66007,7 +66017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>5</v>
       </c>
@@ -66144,17 +66154,17 @@
         <v>5.9113558098403615E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>124</v>
       </c>
       <c r="E29" s="22">
         <f>'SYVbT-passenger'!G3/SUM('SYVbT-passenger'!3:3)*3</f>
-        <v>2.1823637453696615E-2</v>
+        <v>2.1496445375763083E-2</v>
       </c>
       <c r="F29" s="22">
         <f>F36*($E$29/$E$36)*3</f>
-        <v>0.54238648186292071</v>
+        <v>0.53425472287359943</v>
       </c>
       <c r="G29" s="7" t="str">
         <f>IF(E29=F29,"n/a",IF(OR(C29="battery electric vehicle",C29="natural gas vehicle",C29="plugin hybrid vehicle",C29="hydrogen vehicle"),"s-curve","linear"))</f>
@@ -66162,126 +66172,126 @@
       </c>
       <c r="I29" s="22">
         <f t="shared" si="1"/>
-        <v>2.1823637453696615E-2</v>
+        <v>2.1496445375763083E-2</v>
       </c>
       <c r="J29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,J$9))</f>
-        <v>2.1823637453692868E-2</v>
+        <v>2.1496445375760231E-2</v>
       </c>
       <c r="K29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,K$9))</f>
-        <v>4.0415167611165259E-2</v>
+        <v>3.9809241000682505E-2</v>
       </c>
       <c r="L29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,L$9))</f>
-        <v>5.900669776863765E-2</v>
+        <v>5.8122036625604778E-2</v>
       </c>
       <c r="M29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,M$9))</f>
-        <v>7.7598227926110042E-2</v>
+        <v>7.6434832250534157E-2</v>
       </c>
       <c r="N29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,N$9))</f>
-        <v>9.6189758083582433E-2</v>
+        <v>9.4747627875456431E-2</v>
       </c>
       <c r="O29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,O$9))</f>
-        <v>0.11478128824105482</v>
+        <v>0.1130604235003787</v>
       </c>
       <c r="P29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,P$9))</f>
-        <v>0.13337281839852722</v>
+        <v>0.13137321912530098</v>
       </c>
       <c r="Q29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Q$9))</f>
-        <v>0.15196434855599961</v>
+        <v>0.14968601475022325</v>
       </c>
       <c r="R29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,R$9))</f>
-        <v>0.170555878713472</v>
+        <v>0.16799881037514552</v>
       </c>
       <c r="S29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,S$9))</f>
-        <v>0.18914740887094439</v>
+        <v>0.1863116060000678</v>
       </c>
       <c r="T29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,T$9))</f>
-        <v>0.20773893902841678</v>
+        <v>0.20462440162499007</v>
       </c>
       <c r="U29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,U$9))</f>
-        <v>0.22633046918588917</v>
+        <v>0.22293719724991234</v>
       </c>
       <c r="V29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,V$9))</f>
-        <v>0.24492199934336156</v>
+        <v>0.24124999287483462</v>
       </c>
       <c r="W29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,W$9))</f>
-        <v>0.26351352950083395</v>
+        <v>0.25956278849975689</v>
       </c>
       <c r="X29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,X$9))</f>
-        <v>0.28210505965830635</v>
+        <v>0.27787558412467916</v>
       </c>
       <c r="Y29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Y$9))</f>
-        <v>0.30069658981577874</v>
+        <v>0.29618837974960144</v>
       </c>
       <c r="Z29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,Z$9))</f>
-        <v>0.31928811997325113</v>
+        <v>0.31450117537452371</v>
       </c>
       <c r="AA29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AA$9))</f>
-        <v>0.33787965013072352</v>
+        <v>0.33281397099944598</v>
       </c>
       <c r="AB29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AB$9))</f>
-        <v>0.35647118028819591</v>
+        <v>0.35112676662436826</v>
       </c>
       <c r="AC29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AC$9))</f>
-        <v>0.3750627104456683</v>
+        <v>0.36943956224929764</v>
       </c>
       <c r="AD29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AD$9))</f>
-        <v>0.39365424060314069</v>
+        <v>0.38775235787421991</v>
       </c>
       <c r="AE29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AE$9))</f>
-        <v>0.41224577076061308</v>
+        <v>0.40606515349914218</v>
       </c>
       <c r="AF29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AF$9))</f>
-        <v>0.43083730091808548</v>
+        <v>0.42437794912406446</v>
       </c>
       <c r="AG29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AG$9))</f>
-        <v>0.44942883107555787</v>
+        <v>0.44269074474898673</v>
       </c>
       <c r="AH29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AH$9))</f>
-        <v>0.46802036123303026</v>
+        <v>0.461003540373909</v>
       </c>
       <c r="AI29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AI$9))</f>
-        <v>0.48661189139050265</v>
+        <v>0.47931633599883128</v>
       </c>
       <c r="AJ29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AJ$9))</f>
-        <v>0.50520342154797504</v>
+        <v>0.49762913162375355</v>
       </c>
       <c r="AK29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AK$9))</f>
-        <v>0.52379495170544743</v>
+        <v>0.51594192724867582</v>
       </c>
       <c r="AL29">
         <f>IF($G29="s-curve",$E29+($F29-$E29)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E29:$F29,$E$9:$F$9,AL$9))</f>
-        <v>0.54238648186291982</v>
-      </c>
-    </row>
-    <row r="30" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>0.5342547228735981</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
       <c r="B30" s="23"/>
       <c r="C30" s="23" t="s">
@@ -66290,7 +66300,7 @@
       <c r="D30" s="23"/>
       <c r="E30" s="26">
         <f>'SYVbT-passenger'!H3/SUM('SYVbT-passenger'!3:3)</f>
-        <v>8.5993749223261043E-5</v>
+        <v>8.470448323552864E-5</v>
       </c>
       <c r="F30" s="26">
         <v>0.05</v>
@@ -66301,126 +66311,126 @@
       </c>
       <c r="I30" s="22">
         <f t="shared" si="1"/>
-        <v>8.5993749223261043E-5</v>
+        <v>8.470448323552864E-5</v>
       </c>
       <c r="J30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,J$9))</f>
-        <v>8.2342485951046606E-4</v>
+        <v>8.2215464117929744E-4</v>
       </c>
       <c r="K30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,K$9))</f>
-        <v>1.0763028936513275E-3</v>
+        <v>1.0750392070949643E-3</v>
       </c>
       <c r="L30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,L$9))</f>
-        <v>1.4135562528708127E-3</v>
+        <v>1.4123012774822749E-3</v>
       </c>
       <c r="M30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,M$9))</f>
-        <v>1.861494312925186E-3</v>
+        <v>1.860250907661926E-3</v>
       </c>
       <c r="N30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,N$9))</f>
-        <v>2.4532090794568743E-3</v>
+        <v>2.4519809580343683E-3</v>
       </c>
       <c r="O30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,O$9))</f>
-        <v>3.229246237084574E-3</v>
+        <v>3.2280381605029394E-3</v>
       </c>
       <c r="P30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,P$9))</f>
-        <v>4.2374762419148592E-3</v>
+        <v>4.2362942076558247E-3</v>
       </c>
       <c r="Q30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Q$9))</f>
-        <v>5.5314531643209574E-3</v>
+        <v>5.530304553154162E-3</v>
       </c>
       <c r="R30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,R$9))</f>
-        <v>7.1663486893455471E-3</v>
+        <v>7.1652423071111148E-3</v>
       </c>
       <c r="S30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,S$9))</f>
-        <v>9.1915824847949544E-3</v>
+        <v>9.1905284138303605E-3</v>
       </c>
       <c r="T30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,T$9))</f>
-        <v>1.1639849152553195E-2</v>
+        <v>1.1638858319689102E-2</v>
       </c>
       <c r="U30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,U$9))</f>
-        <v>1.4513662081988942E-2</v>
+        <v>1.4512745478976212E-2</v>
       </c>
       <c r="V30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,V$9))</f>
-        <v>1.7772707095192228E-2</v>
+        <v>1.7771874672476845E-2</v>
       </c>
       <c r="W30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,W$9))</f>
-        <v>2.1327272625150932E-2</v>
+        <v>2.1326532015952099E-2</v>
       </c>
       <c r="X30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,X$9))</f>
-        <v>2.5042996874611631E-2</v>
+        <v>2.5042352241617768E-2</v>
       </c>
       <c r="Y30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Y$9))</f>
-        <v>2.8758721124072337E-2</v>
+        <v>2.8758172467283436E-2</v>
       </c>
       <c r="Z30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,Z$9))</f>
-        <v>3.2313286654031034E-2</v>
+        <v>3.2312829810758684E-2</v>
       </c>
       <c r="AA30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AA$9))</f>
-        <v>3.5572331667234322E-2</v>
+        <v>3.5571959004259315E-2</v>
       </c>
       <c r="AB30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AB$9))</f>
-        <v>3.8446144596670069E-2</v>
+        <v>3.8445846163546425E-2</v>
       </c>
       <c r="AC30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AC$9))</f>
-        <v>4.0894411264428311E-2</v>
+        <v>4.0894176069405173E-2</v>
       </c>
       <c r="AD30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AD$9))</f>
-        <v>4.291964505987772E-2</v>
+        <v>4.2919462176124419E-2</v>
       </c>
       <c r="AE30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AE$9))</f>
-        <v>4.4554540584902311E-2</v>
+        <v>4.4554399930081368E-2</v>
       </c>
       <c r="AF30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AF$9))</f>
-        <v>4.5848517507308409E-2</v>
+        <v>4.5848410275579711E-2</v>
       </c>
       <c r="AG30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AG$9))</f>
-        <v>4.685674751213869E-2</v>
+        <v>4.6856666322732596E-2</v>
       </c>
       <c r="AH30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AH$9))</f>
-        <v>4.7632784669766393E-2</v>
+        <v>4.7632723525201169E-2</v>
       </c>
       <c r="AI30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AI$9))</f>
-        <v>4.8224499436298078E-2</v>
+        <v>4.822445357557361E-2</v>
       </c>
       <c r="AJ30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AJ$9))</f>
-        <v>4.8672437496352451E-2</v>
+        <v>4.8672403205753251E-2</v>
       </c>
       <c r="AK30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AK$9))</f>
-        <v>4.9009690855571941E-2</v>
+        <v>4.900966527614057E-2</v>
       </c>
       <c r="AL30">
         <f>IF($G30="s-curve",$E30+($F30-$E30)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E30:$F30,$E$9:$F$9,AL$9))</f>
-        <v>4.9262568889712796E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
+        <v>4.9262549842056233E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -66561,7 +66571,7 @@
         <v>0.99924940887163149</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
         <v>2</v>
       </c>
@@ -66698,7 +66708,7 @@
         <v>5.2146832307325378E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C33" t="s">
         <v>3</v>
       </c>
@@ -66833,7 +66843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>4</v>
       </c>
@@ -66968,7 +66978,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C35" t="s">
         <v>5</v>
       </c>
@@ -67103,7 +67113,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C36" t="s">
         <v>124</v>
       </c>
@@ -67240,7 +67250,7 @@
         <v>6.1785980743152003E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="23"/>
       <c r="B37" s="23"/>
       <c r="C37" s="23" t="s">
@@ -67378,7 +67388,7 @@
         <v>0.14889194762300451</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -67519,7 +67529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
         <v>2</v>
       </c>
@@ -67654,7 +67664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>3</v>
       </c>
@@ -67789,7 +67799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C41" t="s">
         <v>4</v>
       </c>
@@ -67924,7 +67934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>5</v>
       </c>
@@ -68059,7 +68069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>124</v>
       </c>
@@ -68194,7 +68204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="23"/>
       <c r="B44" s="23"/>
       <c r="C44" s="23" t="s">
@@ -68332,7 +68342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -68473,7 +68483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>2</v>
       </c>
@@ -68608,7 +68618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>3</v>
       </c>
@@ -68743,7 +68753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>4</v>
       </c>
@@ -68878,7 +68888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>5</v>
       </c>
@@ -69013,7 +69023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>124</v>
       </c>
@@ -69148,7 +69158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="23"/>
       <c r="B51" s="23"/>
       <c r="C51" s="23" t="s">
@@ -69286,7 +69296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -69298,7 +69308,7 @@
       </c>
       <c r="E52" s="22">
         <f>'SYVbT-passenger'!B5/SUM('SYVbT-passenger'!B5:H5)</f>
-        <v>0.75216927859794647</v>
+        <v>0.93664816809218165</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -69309,126 +69319,126 @@
       </c>
       <c r="I52" s="22">
         <f t="shared" si="2"/>
-        <v>0.75216927859794647</v>
+        <v>0.93664816809218165</v>
       </c>
       <c r="J52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,J$9))</f>
-        <v>0.75583073753050711</v>
+        <v>0.93758413006461472</v>
       </c>
       <c r="K52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,K$9))</f>
-        <v>0.75708631588086017</v>
+        <v>0.93790508780604664</v>
       </c>
       <c r="L52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,L$9))</f>
-        <v>0.75876083070322697</v>
+        <v>0.93833313635851656</v>
       </c>
       <c r="M52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,M$9))</f>
-        <v>0.76098491209651287</v>
+        <v>0.93890166809574294</v>
       </c>
       <c r="N52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,N$9))</f>
-        <v>0.76392286696066514</v>
+        <v>0.93965268403780833</v>
       </c>
       <c r="O52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,O$9))</f>
-        <v>0.76777601085866032</v>
+        <v>0.94063764555977569</v>
       </c>
       <c r="P52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,P$9))</f>
-        <v>0.77278202797098927</v>
+        <v>0.94191731077978458</v>
       </c>
       <c r="Q52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Q$9))</f>
-        <v>0.77920682249752604</v>
+        <v>0.94355965157024346</v>
       </c>
       <c r="R52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,R$9))</f>
-        <v>0.78732433034388383</v>
+        <v>0.94563469291170243</v>
       </c>
       <c r="S52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,S$9))</f>
-        <v>0.79737992776502331</v>
+        <v>0.94820515921205761</v>
       </c>
       <c r="T52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,T$9))</f>
-        <v>0.80953594849008148</v>
+        <v>0.95131254709877777</v>
       </c>
       <c r="U52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,U$9))</f>
-        <v>0.82380487188401408</v>
+        <v>0.95496004661475364</v>
       </c>
       <c r="V52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,V$9))</f>
-        <v>0.83998653185027594</v>
+        <v>0.95909649021776056</v>
       </c>
       <c r="W52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,W$9))</f>
-        <v>0.8576354966545553</v>
+        <v>0.96360801423424369</v>
       </c>
       <c r="X52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,X$9))</f>
-        <v>0.87608463929897318</v>
+        <v>0.96832408404609083</v>
       </c>
       <c r="Y52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Y$9))</f>
-        <v>0.89453378194339117</v>
+        <v>0.97304015385793796</v>
       </c>
       <c r="Z52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,Z$9))</f>
-        <v>0.91218274674767053</v>
+        <v>0.9775516778744211</v>
       </c>
       <c r="AA52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AA$9))</f>
-        <v>0.92836440671393228</v>
+        <v>0.98168812147742801</v>
       </c>
       <c r="AB52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AB$9))</f>
-        <v>0.94263333010786499</v>
+        <v>0.98533562099340388</v>
       </c>
       <c r="AC52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AC$9))</f>
-        <v>0.95478935083292327</v>
+        <v>0.98844300888012404</v>
       </c>
       <c r="AD52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AD$9))</f>
-        <v>0.96484494825406264</v>
+        <v>0.99101347518047922</v>
       </c>
       <c r="AE52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AE$9))</f>
-        <v>0.97296245610042043</v>
+        <v>0.99308851652193819</v>
       </c>
       <c r="AF52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AF$9))</f>
-        <v>0.9793872506269572</v>
+        <v>0.99473085731239708</v>
       </c>
       <c r="AG52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AG$9))</f>
-        <v>0.98439326773928615</v>
+        <v>0.99601052253240596</v>
       </c>
       <c r="AH52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AH$9))</f>
-        <v>0.98824641163728133</v>
+        <v>0.99699548405437333</v>
       </c>
       <c r="AI52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AI$9))</f>
-        <v>0.9911843665014336</v>
+        <v>0.99774649999643872</v>
       </c>
       <c r="AJ52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AJ$9))</f>
-        <v>0.99340844789471949</v>
+        <v>0.99831503173366509</v>
       </c>
       <c r="AK52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AK$9))</f>
-        <v>0.99508296271708629</v>
+        <v>0.99874308028613501</v>
       </c>
       <c r="AL52">
         <f>IF($G52="s-curve",$E52+($F52-$E52)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E52:$F52,$E$9:$F$9,AL$9))</f>
-        <v>0.99633854106743935</v>
-      </c>
-    </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.35">
+        <v>0.99906403802756694</v>
+      </c>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>2</v>
       </c>
@@ -69563,7 +69573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>3</v>
       </c>
@@ -69698,13 +69708,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>4</v>
       </c>
       <c r="E55" s="22">
         <f>1-E52</f>
-        <v>0.24783072140205353</v>
+        <v>6.3351831907818346E-2</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -69715,126 +69725,126 @@
       </c>
       <c r="I55" s="22">
         <f t="shared" si="2"/>
-        <v>0.24783072140205353</v>
+        <v>6.3351831907818346E-2</v>
       </c>
       <c r="J55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:J$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,J$9))</f>
-        <v>0.2478307214020532</v>
+        <v>6.3351831907809242E-2</v>
       </c>
       <c r="K55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:K$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,K$9))</f>
-        <v>0.27469390992341403</v>
+        <v>9.6803552196817577E-2</v>
       </c>
       <c r="L55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:L$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,L$9))</f>
-        <v>0.30155709844476775</v>
+        <v>0.13025527248582591</v>
       </c>
       <c r="M55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:M$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,M$9))</f>
-        <v>0.32842028696612147</v>
+        <v>0.16370699277483425</v>
       </c>
       <c r="N55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:N$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,N$9))</f>
-        <v>0.35528347548747519</v>
+        <v>0.19715871306384258</v>
       </c>
       <c r="O55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:O$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,O$9))</f>
-        <v>0.38214666400883601</v>
+        <v>0.23061043335285092</v>
       </c>
       <c r="P55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:P$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,P$9))</f>
-        <v>0.40900985253018973</v>
+        <v>0.26406215364185925</v>
       </c>
       <c r="Q55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Q$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Q$9))</f>
-        <v>0.43587304105154345</v>
+        <v>0.29751387393085338</v>
       </c>
       <c r="R55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:R$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,R$9))</f>
-        <v>0.46273622957289717</v>
+        <v>0.33096559421986171</v>
       </c>
       <c r="S55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:S$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,S$9))</f>
-        <v>0.48959941809425089</v>
+        <v>0.36441731450887005</v>
       </c>
       <c r="T55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:T$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,T$9))</f>
-        <v>0.51646260661561172</v>
+        <v>0.39786903479787838</v>
       </c>
       <c r="U55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:U$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,U$9))</f>
-        <v>0.54332579513696544</v>
+        <v>0.43132075508688672</v>
       </c>
       <c r="V55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:V$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,V$9))</f>
-        <v>0.57018898365831916</v>
+        <v>0.46477247537589506</v>
       </c>
       <c r="W55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:W$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,W$9))</f>
-        <v>0.59705217217967288</v>
+        <v>0.49822419566490339</v>
       </c>
       <c r="X55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:X$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,X$9))</f>
-        <v>0.6239153607010266</v>
+        <v>0.53167591595391173</v>
       </c>
       <c r="Y55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Y$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Y$9))</f>
-        <v>0.65077854922238743</v>
+        <v>0.56512763624290585</v>
       </c>
       <c r="Z55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:Z$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,Z$9))</f>
-        <v>0.67764173774374115</v>
+        <v>0.59857935653191419</v>
       </c>
       <c r="AA55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AA$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AA$9))</f>
-        <v>0.70450492626509487</v>
+        <v>0.63203107682092252</v>
       </c>
       <c r="AB55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AB$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AB$9))</f>
-        <v>0.73136811478644859</v>
+        <v>0.66548279710993086</v>
       </c>
       <c r="AC55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AC$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AC$9))</f>
-        <v>0.75823130330780941</v>
+        <v>0.69893451739893919</v>
       </c>
       <c r="AD55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AD$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AD$9))</f>
-        <v>0.78509449182916313</v>
+        <v>0.73238623768794753</v>
       </c>
       <c r="AE55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AE$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AE$9))</f>
-        <v>0.81195768035051685</v>
+        <v>0.76583795797695586</v>
       </c>
       <c r="AF55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AF$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AF$9))</f>
-        <v>0.83882086887187057</v>
+        <v>0.7992896782659642</v>
       </c>
       <c r="AG55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AG$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AG$9))</f>
-        <v>0.86568405739322429</v>
+        <v>0.83274139855495832</v>
       </c>
       <c r="AH55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AH$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AH$9))</f>
-        <v>0.89254724591458512</v>
+        <v>0.86619311884396666</v>
       </c>
       <c r="AI55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AI$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AI$9))</f>
-        <v>0.91941043443593884</v>
+        <v>0.89964483913297499</v>
       </c>
       <c r="AJ55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AJ$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AJ$9))</f>
-        <v>0.94627362295729256</v>
+        <v>0.93309655942198333</v>
       </c>
       <c r="AK55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AK$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AK$9))</f>
-        <v>0.97313681147864628</v>
+        <v>0.96654827971099166</v>
       </c>
       <c r="AL55">
         <f>IF($G55="s-curve",$E55+($F55-$E55)*$I$2/(1+EXP($I$3*(COUNT($I$9:AL$9)+$I$4))),TREND($E55:$F55,$E$9:$F$9,AL$9))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>5</v>
       </c>
@@ -69969,7 +69979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>124</v>
       </c>
@@ -70104,7 +70114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="23"/>
       <c r="B58" s="23"/>
       <c r="C58" s="23" t="s">
@@ -70242,7 +70252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>15</v>
       </c>
@@ -70383,7 +70393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>2</v>
       </c>
@@ -70518,7 +70528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>3</v>
       </c>
@@ -70653,7 +70663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>4</v>
       </c>
@@ -70788,7 +70798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>5</v>
       </c>
@@ -70923,7 +70933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>124</v>
       </c>
@@ -71058,7 +71068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="23"/>
       <c r="B65" s="23"/>
       <c r="C65" s="23" t="s">
@@ -71196,7 +71206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>16</v>
       </c>
@@ -71337,7 +71347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>2</v>
       </c>
@@ -71472,7 +71482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>3</v>
       </c>
@@ -71607,7 +71617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>4</v>
       </c>
@@ -71742,7 +71752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>5</v>
       </c>
@@ -71877,7 +71887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>124</v>
       </c>
@@ -72012,7 +72022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="23"/>
       <c r="B72" s="23"/>
       <c r="C72" s="23" t="s">
@@ -72150,7 +72160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>16</v>
       </c>
@@ -72291,7 +72301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>2</v>
       </c>
@@ -72426,7 +72436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>3</v>
       </c>
@@ -72561,7 +72571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>4</v>
       </c>
@@ -72696,7 +72706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>5</v>
       </c>
@@ -72831,7 +72841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>124</v>
       </c>
@@ -72966,7 +72976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="23"/>
       <c r="B79" s="23"/>
       <c r="C79" s="23" t="s">
@@ -73104,7 +73114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -73246,7 +73256,7 @@
         <v>0.99959043283501392</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>2</v>
       </c>
@@ -73382,7 +73392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>3</v>
       </c>
@@ -73517,7 +73527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>4</v>
       </c>
@@ -73653,7 +73663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>5</v>
       </c>
@@ -73789,7 +73799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>124</v>
       </c>
@@ -73925,7 +73935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="23"/>
       <c r="B86" s="23"/>
       <c r="C86" s="23" t="s">
@@ -74064,7 +74074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -74205,7 +74215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>2</v>
       </c>
@@ -74340,7 +74350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>3</v>
       </c>
@@ -74475,7 +74485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>4</v>
       </c>
@@ -74610,7 +74620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>5</v>
       </c>
@@ -74745,7 +74755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>124</v>
       </c>
@@ -74880,7 +74890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="23"/>
       <c r="B93" s="23"/>
       <c r="C93" s="23" t="s">

--- a/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
+++ b/InputData/trans/TTS/Transportation Technology Shareweights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\ND\trans\TTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E57D70B5-3EB4-4444-9025-E3D64D8E96F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB7E4C36-3284-43F0-931F-94A37BBD1DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="19560" windowHeight="17085" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="555" windowWidth="19605" windowHeight="12645" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -4732,91 +4732,91 @@
                   <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.22583637175876042</c:v>
+                  <c:v>0.2579411882892142</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.23794069854205344</c:v>
+                  <c:v>0.27627957191928759</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.25531073627467749</c:v>
+                  <c:v>0.2996426865499332</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.27980039129574813</c:v>
+                  <c:v>0.32888715966126825</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.31348085192039021</c:v>
+                  <c:v>0.36469629744075793</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35825288915313458</c:v>
+                  <c:v>0.40738008065427683</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.41515313709599611</c:v>
+                  <c:v>0.45665704065968565</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.48347495501936366</c:v>
+                  <c:v>0.51148861284062241</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.56013280215001782</c:v>
+                  <c:v>0.57005612372500036</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.63986719784998236</c:v>
+                  <c:v>0.62994387627499959</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.71652504498063641</c:v>
+                  <c:v>0.68851138715937765</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.78484686290400396</c:v>
+                  <c:v>0.74334295934031447</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.84174711084686549</c:v>
+                  <c:v>0.79261991934572329</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.88651914807960996</c:v>
+                  <c:v>0.83530370255924202</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.92019960870425188</c:v>
+                  <c:v>0.87111284033873182</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.94468926372532258</c:v>
+                  <c:v>0.90035731345006687</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.9620593014579466</c:v>
+                  <c:v>0.92372042808071253</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.97416362824123981</c:v>
+                  <c:v>0.94205881171078576</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.98249498325109563</c:v>
+                  <c:v>0.95625494622724738</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.98818077464538168</c:v>
+                  <c:v>0.96712697743962805</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9920385585064766</c:v>
+                  <c:v>0.97538491251428172</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.99464571926057221</c:v>
+                  <c:v>0.98161810407197958</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.99640298147124717</c:v>
+                  <c:v>0.98630077334741784</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.99758526694023342</c:v>
+                  <c:v>0.98980612042871075</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.99837974368876004</c:v>
+                  <c:v>0.99242316513444306</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.99891318403965701</c:v>
+                  <c:v>0.99437313027600394</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.99927115904447961</c:v>
+                  <c:v>0.99582389944515337</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.99951129651245263</c:v>
+                  <c:v>0.99690207724746327</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.99967234626801127</c:v>
+                  <c:v>0.99770269667543965</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5075,89 +5075,89 @@
                 <c:pt idx="1">
                   <c:v>4.8000000000000001E-2</c:v>
                 </c:pt>
-                <c:pt idx="2" formatCode="General">
-                  <c:v>6.8830969931196209E-2</c:v>
+                <c:pt idx="2">
+                  <c:v>9.9000000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>7.8745282392924873E-2</c:v>
+                  <c:v>0.11695001406416487</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>9.3149431265043575E-2</c:v>
+                  <c:v>0.13877269058395222</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>0.11381977616686616</c:v>
+                  <c:v>0.16657479699442046</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
-                  <c:v>0.14296246564194026</c:v>
+                  <c:v>0.20137571999690912</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="General">
-                  <c:v>0.18304221378526436</c:v>
+                  <c:v>0.2439885939545019</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
-                  <c:v>0.23632093809223015</c:v>
+                  <c:v>0.2947822959785894</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="General">
-                  <c:v>0.30403223314423533</c:v>
+                  <c:v>0.35342187838502587</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
-                  <c:v>0.38533519647304271</c:v>
+                  <c:v>0.41867144928034067</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="General">
-                  <c:v>0.47655803455852103</c:v>
+                  <c:v>0.4883667872327504</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>0.57144196544147907</c:v>
+                  <c:v>0.55963321276724964</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>0.66266480352695722</c:v>
+                  <c:v>0.62932855071965943</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>0.7439677668557646</c:v>
+                  <c:v>0.69457812161497412</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>0.81167906190776995</c:v>
+                  <c:v>0.75321770402141064</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>0.86495778621473574</c:v>
+                  <c:v>0.80401140604549803</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>0.90503753435805978</c:v>
+                  <c:v>0.84662428000309087</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>0.93418022383313393</c:v>
+                  <c:v>0.88142520300557958</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>0.95485056873495655</c:v>
+                  <c:v>0.90922730941604779</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>0.96925471760707527</c:v>
+                  <c:v>0.9310499859358351</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>0.97916903006880374</c:v>
+                  <c:v>0.94794338601042438</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>0.98593512182800402</c:v>
+                  <c:v>0.96088110315315733</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>0.99052588462270719</c:v>
+                  <c:v>0.97070804589199511</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>0.99362840592008095</c:v>
+                  <c:v>0.97812554384565553</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>0.99571954795078399</c:v>
+                  <c:v>0.98369792028342729</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>0.99712646765887769</c:v>
+                  <c:v>0.98786928331016577</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="General">
-                  <c:v>0.99807189498962445</c:v>
+                  <c:v>0.9909835665099872</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="General">
-                  <c:v>0.99870668900719173</c:v>
+                  <c:v>0.99330402502844461</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="General">
-                  <c:v>0.99913267926293059</c:v>
+                  <c:v>0.99503044033973242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7426,7 +7426,7 @@
         <v>1000</v>
       </c>
       <c r="C1" s="49">
-        <v>45310</v>
+        <v>45321</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -8106,115 +8106,115 @@
       </c>
       <c r="D2">
         <f>Data!K10</f>
-        <v>6.8830969931196209E-2</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="E2">
         <f>Data!L10</f>
-        <v>7.8745282392924873E-2</v>
+        <v>0.11695001406416487</v>
       </c>
       <c r="F2">
         <f>Data!M10</f>
-        <v>9.3149431265043575E-2</v>
+        <v>0.13877269058395222</v>
       </c>
       <c r="G2">
         <f>Data!N10</f>
-        <v>0.11381977616686616</v>
+        <v>0.16657479699442046</v>
       </c>
       <c r="H2">
         <f>Data!O10</f>
-        <v>0.14296246564194026</v>
+        <v>0.20137571999690912</v>
       </c>
       <c r="I2">
         <f>Data!P10</f>
-        <v>0.18304221378526436</v>
+        <v>0.2439885939545019</v>
       </c>
       <c r="J2">
         <f>Data!Q10</f>
-        <v>0.23632093809223015</v>
+        <v>0.2947822959785894</v>
       </c>
       <c r="K2">
         <f>Data!R10</f>
-        <v>0.30403223314423533</v>
+        <v>0.35342187838502587</v>
       </c>
       <c r="L2">
         <f>Data!S10</f>
-        <v>0.38533519647304271</v>
+        <v>0.41867144928034067</v>
       </c>
       <c r="M2">
         <f>Data!T10</f>
-        <v>0.47655803455852103</v>
+        <v>0.4883667872327504</v>
       </c>
       <c r="N2">
         <f>Data!U10</f>
-        <v>0.57144196544147907</v>
+        <v>0.55963321276724964</v>
       </c>
       <c r="O2">
         <f>Data!V10</f>
-        <v>0.66266480352695722</v>
+        <v>0.62932855071965943</v>
       </c>
       <c r="P2">
         <f>Data!W10</f>
-        <v>0.7439677668557646</v>
+        <v>0.69457812161497412</v>
       </c>
       <c r="Q2">
         <f>Data!X10</f>
-        <v>0.81167906190776995</v>
+        <v>0.75321770402141064</v>
       </c>
       <c r="R2">
         <f>Data!Y10</f>
-        <v>0.86495778621473574</v>
+        <v>0.80401140604549803</v>
       </c>
       <c r="S2">
         <f>Data!Z10</f>
-        <v>0.90503753435805978</v>
+        <v>0.84662428000309087</v>
       </c>
       <c r="T2">
         <f>Data!AA10</f>
-        <v>0.93418022383313393</v>
+        <v>0.88142520300557958</v>
       </c>
       <c r="U2">
         <f>Data!AB10</f>
-        <v>0.95485056873495655</v>
+        <v>0.90922730941604779</v>
       </c>
       <c r="V2">
         <f>Data!AC10</f>
-        <v>0.96925471760707527</v>
+        <v>0.9310499859358351</v>
       </c>
       <c r="W2">
         <f>Data!AD10</f>
-        <v>0.97916903006880374</v>
+        <v>0.94794338601042438</v>
       </c>
       <c r="X2">
         <f>Data!AE10</f>
-        <v>0.98593512182800402</v>
+        <v>0.96088110315315733</v>
       </c>
       <c r="Y2">
         <f>Data!AF10</f>
-        <v>0.99052588462270719</v>
+        <v>0.97070804589199511</v>
       </c>
       <c r="Z2">
         <f>Data!AG10</f>
-        <v>0.99362840592008095</v>
+        <v>0.97812554384565553</v>
       </c>
       <c r="AA2">
         <f>Data!AH10</f>
-        <v>0.99571954795078399</v>
+        <v>0.98369792028342729</v>
       </c>
       <c r="AB2">
         <f>Data!AI10</f>
-        <v>0.99712646765887769</v>
+        <v>0.98786928331016577</v>
       </c>
       <c r="AC2">
         <f>Data!AJ10</f>
-        <v>0.99807189498962445</v>
+        <v>0.9909835665099872</v>
       </c>
       <c r="AD2">
         <f>Data!AK10</f>
-        <v>0.99870668900719173</v>
+        <v>0.99330402502844461</v>
       </c>
       <c r="AE2">
         <f>Data!AL10</f>
-        <v>0.99913267926293059</v>
+        <v>0.99503044033973242</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -8606,115 +8606,115 @@
       </c>
       <c r="D6">
         <f>Data!K14</f>
-        <v>9.9918866734578053E-3</v>
+        <v>1.2004677525762598E-2</v>
       </c>
       <c r="E6">
         <f>Data!L14</f>
-        <v>1.0903813654420566E-2</v>
+        <v>1.3231241043871491E-2</v>
       </c>
       <c r="F6">
         <f>Data!M14</f>
-        <v>1.2189520543026775E-2</v>
+        <v>1.4766575882216582E-2</v>
       </c>
       <c r="G6">
         <f>Data!N14</f>
-        <v>1.3957744725820488E-2</v>
+        <v>1.664655561563979E-2</v>
       </c>
       <c r="H6">
         <f>Data!O14</f>
-        <v>1.6308276680539566E-2</v>
+        <v>1.8887454234349531E-2</v>
       </c>
       <c r="I6">
         <f>Data!P14</f>
-        <v>1.9295539697539797E-2</v>
+        <v>2.1474494634633495E-2</v>
       </c>
       <c r="J6">
         <f>Data!Q14</f>
-        <v>2.2882435138516594E-2</v>
+        <v>2.435315217413268E-2</v>
       </c>
       <c r="K6">
         <f>Data!R14</f>
-        <v>2.6906972112875932E-2</v>
+        <v>2.742794649556252E-2</v>
       </c>
       <c r="L6">
         <f>Data!S14</f>
-        <v>3.1093027887124074E-2</v>
+        <v>3.0572053504437483E-2</v>
       </c>
       <c r="M6">
         <f>Data!T14</f>
-        <v>3.5117564861483409E-2</v>
+        <v>3.3646847825867326E-2</v>
       </c>
       <c r="N6">
         <f>Data!U14</f>
-        <v>3.8704460302460206E-2</v>
+        <v>3.6525505365366501E-2</v>
       </c>
       <c r="O6">
         <f>Data!V14</f>
-        <v>4.1691723319460437E-2</v>
+        <v>3.9112545765650472E-2</v>
       </c>
       <c r="P6">
         <f>Data!W14</f>
-        <v>4.4042255274179515E-2</v>
+        <v>4.1353444384360213E-2</v>
       </c>
       <c r="Q6">
         <f>Data!X14</f>
-        <v>4.5810479456973224E-2</v>
+        <v>4.3233424117783421E-2</v>
       </c>
       <c r="R6">
         <f>Data!Y14</f>
-        <v>4.7096186345579438E-2</v>
+        <v>4.4768758956128508E-2</v>
       </c>
       <c r="S6">
         <f>Data!Z14</f>
-        <v>4.8008113326542201E-2</v>
+        <v>4.5995322474237404E-2</v>
       </c>
       <c r="T6">
         <f>Data!AA14</f>
-        <v>4.8643590482665089E-2</v>
+        <v>4.6958087614816256E-2</v>
       </c>
       <c r="U6">
         <f>Data!AB14</f>
-        <v>4.9080986620682519E-2</v>
+        <v>4.7703384676930492E-2</v>
       </c>
       <c r="V6">
         <f>Data!AC14</f>
-        <v>4.9379490668882538E-2</v>
+        <v>4.8274166315580479E-2</v>
       </c>
       <c r="W6">
         <f>Data!AD14</f>
-        <v>4.9582024321590021E-2</v>
+        <v>4.8707707906999784E-2</v>
       </c>
       <c r="X6">
         <f>Data!AE14</f>
-        <v>4.9718900261180046E-2</v>
+        <v>4.9034950463778926E-2</v>
       </c>
       <c r="Y6">
         <f>Data!AF14</f>
-        <v>4.9811156527240476E-2</v>
+        <v>4.9280790600739442E-2</v>
       </c>
       <c r="Z6">
         <f>Data!AG14</f>
-        <v>4.9873226514362254E-2</v>
+        <v>4.9464821322507319E-2</v>
       </c>
       <c r="AA6">
         <f>Data!AH14</f>
-        <v>4.9914936543659902E-2</v>
+        <v>4.9602216169558261E-2</v>
       </c>
       <c r="AB6">
         <f>Data!AI14</f>
-        <v>4.9942942162081991E-2</v>
+        <v>4.9704589339490207E-2</v>
       </c>
       <c r="AC6">
         <f>Data!AJ14</f>
-        <v>4.9961735849835175E-2</v>
+        <v>4.9780754720870554E-2</v>
       </c>
       <c r="AD6">
         <f>Data!AK14</f>
-        <v>4.9974343066903758E-2</v>
+        <v>4.9837359055491817E-2</v>
       </c>
       <c r="AE6">
         <f>Data!AL14</f>
-        <v>4.9982798179070587E-2</v>
+        <v>4.9879391575460584E-2</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
@@ -9118,119 +9118,119 @@
       </c>
       <c r="C2">
         <f>Data!J17</f>
-        <v>0.22583637175876042</v>
+        <v>0.2579411882892142</v>
       </c>
       <c r="D2">
         <f>Data!K17</f>
-        <v>0.23794069854205344</v>
+        <v>0.27627957191928759</v>
       </c>
       <c r="E2">
         <f>Data!L17</f>
-        <v>0.25531073627467749</v>
+        <v>0.2996426865499332</v>
       </c>
       <c r="F2">
         <f>Data!M17</f>
-        <v>0.27980039129574813</v>
+        <v>0.32888715966126825</v>
       </c>
       <c r="G2">
         <f>Data!N17</f>
-        <v>0.31348085192039021</v>
+        <v>0.36469629744075793</v>
       </c>
       <c r="H2">
         <f>Data!O17</f>
-        <v>0.35825288915313458</v>
+        <v>0.40738008065427683</v>
       </c>
       <c r="I2">
         <f>Data!P17</f>
-        <v>0.41515313709599611</v>
+        <v>0.45665704065968565</v>
       </c>
       <c r="J2">
         <f>Data!Q17</f>
-        <v>0.48347495501936366</v>
+        <v>0.51148861284062241</v>
       </c>
       <c r="K2">
         <f>Data!R17</f>
-        <v>0.56013280215001782</v>
+        <v>0.57005612372500036</v>
       </c>
       <c r="L2">
         <f>Data!S17</f>
-        <v>0.63986719784998236</v>
+        <v>0.62994387627499959</v>
       </c>
       <c r="M2">
         <f>Data!T17</f>
-        <v>0.71652504498063641</v>
+        <v>0.68851138715937765</v>
       </c>
       <c r="N2">
         <f>Data!U17</f>
-        <v>0.78484686290400396</v>
+        <v>0.74334295934031447</v>
       </c>
       <c r="O2">
         <f>Data!V17</f>
-        <v>0.84174711084686549</v>
+        <v>0.79261991934572329</v>
       </c>
       <c r="P2">
         <f>Data!W17</f>
-        <v>0.88651914807960996</v>
+        <v>0.83530370255924202</v>
       </c>
       <c r="Q2">
         <f>Data!X17</f>
-        <v>0.92019960870425188</v>
+        <v>0.87111284033873182</v>
       </c>
       <c r="R2">
         <f>Data!Y17</f>
-        <v>0.94468926372532258</v>
+        <v>0.90035731345006687</v>
       </c>
       <c r="S2">
         <f>Data!Z17</f>
-        <v>0.9620593014579466</v>
+        <v>0.92372042808071253</v>
       </c>
       <c r="T2">
         <f>Data!AA17</f>
-        <v>0.97416362824123981</v>
+        <v>0.94205881171078576</v>
       </c>
       <c r="U2">
         <f>Data!AB17</f>
-        <v>0.98249498325109563</v>
+        <v>0.95625494622724738</v>
       </c>
       <c r="V2">
         <f>Data!AC17</f>
-        <v>0.98818077464538168</v>
+        <v>0.96712697743962805</v>
       </c>
       <c r="W2">
         <f>Data!AD17</f>
-        <v>0.9920385585064766</v>
+        <v>0.97538491251428172</v>
       </c>
       <c r="X2">
         <f>Data!AE17</f>
-        <v>0.99464571926057221</v>
+        <v>0.98161810407197958</v>
       </c>
       <c r="Y2">
         <f>Data!AF17</f>
-        <v>0.99640298147124717</v>
+        <v>0.98630077334741784</v>
       </c>
       <c r="Z2">
         <f>Data!AG17</f>
-        <v>0.99758526694023342</v>
+        <v>0.98980612042871075</v>
       </c>
       <c r="AA2">
         <f>Data!AH17</f>
-        <v>0.99837974368876004</v>
+        <v>0.99242316513444306</v>
       </c>
       <c r="AB2">
         <f>Data!AI17</f>
-        <v>0.99891318403965701</v>
+        <v>0.99437313027600394</v>
       </c>
       <c r="AC2">
         <f>Data!AJ17</f>
-        <v>0.99927115904447961</v>
+        <v>0.99582389944515337</v>
       </c>
       <c r="AD2">
         <f>Data!AK17</f>
-        <v>0.99951129651245263</v>
+        <v>0.99690207724746327</v>
       </c>
       <c r="AE2">
         <f>Data!AL17</f>
-        <v>0.99967234626801127</v>
+        <v>0.99770269667543965</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -10138,115 +10138,115 @@
       </c>
       <c r="D2">
         <f>Data!K24</f>
-        <v>0.60875250837445216</v>
+        <v>0.62187252688637629</v>
       </c>
       <c r="E2">
         <f>Data!L24</f>
-        <v>0.61291818587938018</v>
+        <v>0.6289705941446071</v>
       </c>
       <c r="F2">
         <f>Data!M24</f>
-        <v>0.61897034927102668</v>
+        <v>0.63813978595964382</v>
       </c>
       <c r="G2">
         <f>Data!N24</f>
-        <v>0.62765536813733869</v>
+        <v>0.64982134327496655</v>
       </c>
       <c r="H2">
         <f>Data!O24</f>
-        <v>0.63990019564787404</v>
+        <v>0.66444357983063407</v>
       </c>
       <c r="I2">
         <f>Data!P24</f>
-        <v>0.65674042596019511</v>
+        <v>0.68234814872037897</v>
       </c>
       <c r="J2">
         <f>Data!Q24</f>
-        <v>0.67912644457656723</v>
+        <v>0.70369004032713844</v>
       </c>
       <c r="K2">
         <f>Data!R24</f>
-        <v>0.707576568547998</v>
+        <v>0.72832852032984285</v>
       </c>
       <c r="L2">
         <f>Data!S24</f>
-        <v>0.74173747750968178</v>
+        <v>0.75574430642031121</v>
       </c>
       <c r="M2">
         <f>Data!T24</f>
-        <v>0.78006640107500891</v>
+        <v>0.78502806186250018</v>
       </c>
       <c r="N2">
         <f>Data!U24</f>
-        <v>0.81993359892499118</v>
+        <v>0.8149719381374998</v>
       </c>
       <c r="O2">
         <f>Data!V24</f>
-        <v>0.8582625224903182</v>
+        <v>0.84425569357968877</v>
       </c>
       <c r="P2">
         <f>Data!W24</f>
-        <v>0.89242343145200187</v>
+        <v>0.87167147967015723</v>
       </c>
       <c r="Q2">
         <f>Data!X24</f>
-        <v>0.92087355542343274</v>
+        <v>0.89630995967286164</v>
       </c>
       <c r="R2">
         <f>Data!Y24</f>
-        <v>0.94325957403980487</v>
+        <v>0.91765185127962101</v>
       </c>
       <c r="S2">
         <f>Data!Z24</f>
-        <v>0.96009980435212594</v>
+        <v>0.93555642016936591</v>
       </c>
       <c r="T2">
         <f>Data!AA24</f>
-        <v>0.97234463186266129</v>
+        <v>0.95017865672503343</v>
       </c>
       <c r="U2">
         <f>Data!AB24</f>
-        <v>0.9810296507289733</v>
+        <v>0.96186021404035627</v>
       </c>
       <c r="V2">
         <f>Data!AC24</f>
-        <v>0.9870818141206199</v>
+        <v>0.97102940585539288</v>
       </c>
       <c r="W2">
         <f>Data!AD24</f>
-        <v>0.99124749162554782</v>
+        <v>0.97812747311362369</v>
       </c>
       <c r="X2">
         <f>Data!AE24</f>
-        <v>0.99409038732269073</v>
+        <v>0.98356348871981403</v>
       </c>
       <c r="Y2">
         <f>Data!AF24</f>
-        <v>0.9960192792532383</v>
+        <v>0.98769245625714075</v>
       </c>
       <c r="Z2">
         <f>Data!AG24</f>
-        <v>0.99732285963028611</v>
+        <v>0.99080905203598979</v>
       </c>
       <c r="AA2">
         <f>Data!AH24</f>
-        <v>0.99820149073562359</v>
+        <v>0.99315038667370892</v>
       </c>
       <c r="AB2">
         <f>Data!AI24</f>
-        <v>0.99879263347011671</v>
+        <v>0.99490306021435537</v>
       </c>
       <c r="AC2">
         <f>Data!AJ24</f>
-        <v>0.99918987184438002</v>
+        <v>0.99621158256722153</v>
       </c>
       <c r="AD2">
         <f>Data!AK24</f>
-        <v>0.99945659201982839</v>
+        <v>0.99718656513800186</v>
       </c>
       <c r="AE2">
         <f>Data!AL24</f>
-        <v>0.9996355795222398</v>
+        <v>0.99791194972257657</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -24606,119 +24606,119 @@
       </c>
       <c r="C2">
         <f>Data!J80</f>
-        <v>3.2295464698450495E-2</v>
+        <v>7.2426485361517731E-2</v>
       </c>
       <c r="D2">
         <f>Data!K80</f>
-        <v>4.7425873177566781E-2</v>
+        <v>9.534946489910949E-2</v>
       </c>
       <c r="E2">
         <f>Data!L80</f>
-        <v>6.9138420343346815E-2</v>
+        <v>0.12455335818741645</v>
       </c>
       <c r="F2">
         <f>Data!M80</f>
-        <v>9.9750489119685135E-2</v>
+        <v>0.16110894957658525</v>
       </c>
       <c r="G2">
         <f>Data!N80</f>
-        <v>0.14185106490048777</v>
+        <v>0.20587037180094736</v>
       </c>
       <c r="H2">
         <f>Data!O80</f>
-        <v>0.19781611144141822</v>
+        <v>0.259225100817846</v>
       </c>
       <c r="I2">
         <f>Data!P80</f>
-        <v>0.2689414213699951</v>
+        <v>0.32082130082460703</v>
       </c>
       <c r="J2">
         <f>Data!Q80</f>
-        <v>0.35434369377420455</v>
+        <v>0.38936076605077802</v>
       </c>
       <c r="K2">
         <f>Data!R80</f>
-        <v>0.45016600268752216</v>
+        <v>0.46257015465625045</v>
       </c>
       <c r="L2">
         <f>Data!S80</f>
-        <v>0.54983399731247795</v>
+        <v>0.5374298453437496</v>
       </c>
       <c r="M2">
         <f>Data!T80</f>
-        <v>0.6456563062257954</v>
+        <v>0.61063923394922204</v>
       </c>
       <c r="N2">
         <f>Data!U80</f>
-        <v>0.7310585786300049</v>
+        <v>0.67917869917539297</v>
       </c>
       <c r="O2">
         <f>Data!V80</f>
-        <v>0.8021838885585818</v>
+        <v>0.740774899182154</v>
       </c>
       <c r="P2">
         <f>Data!W80</f>
-        <v>0.85814893509951229</v>
+        <v>0.79412962819905253</v>
       </c>
       <c r="Q2">
         <f>Data!X80</f>
-        <v>0.9002495108803148</v>
+        <v>0.83889105042341472</v>
       </c>
       <c r="R2">
         <f>Data!Y80</f>
-        <v>0.93086157965665328</v>
+        <v>0.87544664181258358</v>
       </c>
       <c r="S2">
         <f>Data!Z80</f>
-        <v>0.95257412682243336</v>
+        <v>0.90465053510089055</v>
       </c>
       <c r="T2">
         <f>Data!AA80</f>
-        <v>0.96770453530154954</v>
+        <v>0.92757351463848225</v>
       </c>
       <c r="U2">
         <f>Data!AB80</f>
-        <v>0.97811872906386943</v>
+        <v>0.94531868278405917</v>
       </c>
       <c r="V2">
         <f>Data!AC80</f>
-        <v>0.98522596830672693</v>
+        <v>0.95890872179953501</v>
       </c>
       <c r="W2">
         <f>Data!AD80</f>
-        <v>0.99004819813309575</v>
+        <v>0.96923114064285198</v>
       </c>
       <c r="X2">
         <f>Data!AE80</f>
-        <v>0.99330714907571527</v>
+        <v>0.97702263008997436</v>
       </c>
       <c r="Y2">
         <f>Data!AF80</f>
-        <v>0.99550372683905886</v>
+        <v>0.98287596668427235</v>
       </c>
       <c r="Z2">
         <f>Data!AG80</f>
-        <v>0.99698158367529166</v>
+        <v>0.98725765053588843</v>
       </c>
       <c r="AA2">
         <f>Data!AH80</f>
-        <v>0.9979746796109501</v>
+        <v>0.99052895641805383</v>
       </c>
       <c r="AB2">
         <f>Data!AI80</f>
-        <v>0.9986414800495711</v>
+        <v>0.99296641284500486</v>
       </c>
       <c r="AC2">
         <f>Data!AJ80</f>
-        <v>0.9990889488055994</v>
+        <v>0.99477987430644166</v>
       </c>
       <c r="AD2">
         <f>Data!AK80</f>
-        <v>0.99938912064056562</v>
+        <v>0.99612759655932892</v>
       </c>
       <c r="AE2">
         <f>Data!AL80</f>
-        <v>0.99959043283501392</v>
+        <v>0.99712837084429951</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -63316,7 +63316,7 @@
         <v>99</v>
       </c>
       <c r="O3" s="19">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="Q3" s="9" t="s">
         <v>99</v>
@@ -63366,6 +63366,12 @@
       </c>
       <c r="G6" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="N6" s="12">
+        <v>2023</v>
+      </c>
+      <c r="O6" s="22">
+        <v>9.9000000000000005E-2</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
@@ -63565,117 +63571,117 @@
         <f>E10</f>
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="K10">
-        <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,K$9))</f>
-        <v>6.8830969931196209E-2</v>
+      <c r="K10" s="22">
+        <f>O6</f>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="L10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,L$9))</f>
-        <v>7.8745282392924873E-2</v>
+        <v>0.11695001406416487</v>
       </c>
       <c r="M10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,M$9))</f>
-        <v>9.3149431265043575E-2</v>
+        <v>0.13877269058395222</v>
       </c>
       <c r="N10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,N$9))</f>
-        <v>0.11381977616686616</v>
+        <v>0.16657479699442046</v>
       </c>
       <c r="O10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,O$9))</f>
-        <v>0.14296246564194026</v>
+        <v>0.20137571999690912</v>
       </c>
       <c r="P10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,P$9))</f>
-        <v>0.18304221378526436</v>
+        <v>0.2439885939545019</v>
       </c>
       <c r="Q10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Q$9))</f>
-        <v>0.23632093809223015</v>
+        <v>0.2947822959785894</v>
       </c>
       <c r="R10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,R$9))</f>
-        <v>0.30403223314423533</v>
+        <v>0.35342187838502587</v>
       </c>
       <c r="S10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,S$9))</f>
-        <v>0.38533519647304271</v>
+        <v>0.41867144928034067</v>
       </c>
       <c r="T10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,T$9))</f>
-        <v>0.47655803455852103</v>
+        <v>0.4883667872327504</v>
       </c>
       <c r="U10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,U$9))</f>
-        <v>0.57144196544147907</v>
+        <v>0.55963321276724964</v>
       </c>
       <c r="V10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,V$9))</f>
-        <v>0.66266480352695722</v>
+        <v>0.62932855071965943</v>
       </c>
       <c r="W10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,W$9))</f>
-        <v>0.7439677668557646</v>
+        <v>0.69457812161497412</v>
       </c>
       <c r="X10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,X$9))</f>
-        <v>0.81167906190776995</v>
+        <v>0.75321770402141064</v>
       </c>
       <c r="Y10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Y$9))</f>
-        <v>0.86495778621473574</v>
+        <v>0.80401140604549803</v>
       </c>
       <c r="Z10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,Z$9))</f>
-        <v>0.90503753435805978</v>
+        <v>0.84662428000309087</v>
       </c>
       <c r="AA10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AA$9))</f>
-        <v>0.93418022383313393</v>
+        <v>0.88142520300557958</v>
       </c>
       <c r="AB10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AB$9))</f>
-        <v>0.95485056873495655</v>
+        <v>0.90922730941604779</v>
       </c>
       <c r="AC10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AC$9))</f>
-        <v>0.96925471760707527</v>
+        <v>0.9310499859358351</v>
       </c>
       <c r="AD10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AD$9))</f>
-        <v>0.97916903006880374</v>
+        <v>0.94794338601042438</v>
       </c>
       <c r="AE10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AE$9))</f>
-        <v>0.98593512182800402</v>
+        <v>0.96088110315315733</v>
       </c>
       <c r="AF10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AF$9))</f>
-        <v>0.99052588462270719</v>
+        <v>0.97070804589199511</v>
       </c>
       <c r="AG10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AG$9))</f>
-        <v>0.99362840592008095</v>
+        <v>0.97812554384565553</v>
       </c>
       <c r="AH10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AH$9))</f>
-        <v>0.99571954795078399</v>
+        <v>0.98369792028342729</v>
       </c>
       <c r="AI10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AI$9))</f>
-        <v>0.99712646765887769</v>
+        <v>0.98786928331016577</v>
       </c>
       <c r="AJ10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AJ$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AJ$9))</f>
-        <v>0.99807189498962445</v>
+        <v>0.9909835665099872</v>
       </c>
       <c r="AK10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AK$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AK$9))</f>
-        <v>0.99870668900719173</v>
+        <v>0.99330402502844461</v>
       </c>
       <c r="AL10">
         <f>IF($G10="s-curve",$E10+($F10-$E10)*$O$2/(1+EXP($O$3*(COUNT($K$9:AL$9)+$O$4))),TREND($E10:$F10,$E$9:$F$9,AL$9))</f>
-        <v>0.99913267926293059</v>
+        <v>0.99503044033973242</v>
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
@@ -64114,115 +64120,115 @@
       </c>
       <c r="K14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,K$9))</f>
-        <v>9.9918866734578053E-3</v>
+        <v>1.2004677525762598E-2</v>
       </c>
       <c r="L14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,L$9))</f>
-        <v>1.0903813654420566E-2</v>
+        <v>1.3231241043871491E-2</v>
       </c>
       <c r="M14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,M$9))</f>
-        <v>1.2189520543026775E-2</v>
+        <v>1.4766575882216582E-2</v>
       </c>
       <c r="N14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,N$9))</f>
-        <v>1.3957744725820488E-2</v>
+        <v>1.664655561563979E-2</v>
       </c>
       <c r="O14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,O$9))</f>
-        <v>1.6308276680539566E-2</v>
+        <v>1.8887454234349531E-2</v>
       </c>
       <c r="P14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,P$9))</f>
-        <v>1.9295539697539797E-2</v>
+        <v>2.1474494634633495E-2</v>
       </c>
       <c r="Q14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Q$9))</f>
-        <v>2.2882435138516594E-2</v>
+        <v>2.435315217413268E-2</v>
       </c>
       <c r="R14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,R$9))</f>
-        <v>2.6906972112875932E-2</v>
+        <v>2.742794649556252E-2</v>
       </c>
       <c r="S14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,S$9))</f>
-        <v>3.1093027887124074E-2</v>
+        <v>3.0572053504437483E-2</v>
       </c>
       <c r="T14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,T$9))</f>
-        <v>3.5117564861483409E-2</v>
+        <v>3.3646847825867326E-2</v>
       </c>
       <c r="U14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,U$9))</f>
-        <v>3.8704460302460206E-2</v>
+        <v>3.6525505365366501E-2</v>
       </c>
       <c r="V14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,V$9))</f>
-        <v>4.1691723319460437E-2</v>
+        <v>3.9112545765650472E-2</v>
       </c>
       <c r="W14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,W$9))</f>
-        <v>4.4042255274179515E-2</v>
+        <v>4.1353444384360213E-2</v>
       </c>
       <c r="X14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,X$9))</f>
-        <v>4.5810479456973224E-2</v>
+        <v>4.3233424117783421E-2</v>
       </c>
       <c r="Y14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Y$9))</f>
-        <v>4.7096186345579438E-2</v>
+        <v>4.4768758956128508E-2</v>
       </c>
       <c r="Z14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,Z$9))</f>
-        <v>4.8008113326542201E-2</v>
+        <v>4.5995322474237404E-2</v>
       </c>
       <c r="AA14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AA$9))</f>
-        <v>4.8643590482665089E-2</v>
+        <v>4.6958087614816256E-2</v>
       </c>
       <c r="AB14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AB$9))</f>
-        <v>4.9080986620682519E-2</v>
+        <v>4.7703384676930492E-2</v>
       </c>
       <c r="AC14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AC$9))</f>
-        <v>4.9379490668882538E-2</v>
+        <v>4.8274166315580479E-2</v>
       </c>
       <c r="AD14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AD$9))</f>
-        <v>4.9582024321590021E-2</v>
+        <v>4.8707707906999784E-2</v>
       </c>
       <c r="AE14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AE$9))</f>
-        <v>4.9718900261180046E-2</v>
+        <v>4.9034950463778926E-2</v>
       </c>
       <c r="AF14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AF$9))</f>
-        <v>4.9811156527240476E-2</v>
+        <v>4.9280790600739442E-2</v>
       </c>
       <c r="AG14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AG$9))</f>
-        <v>4.9873226514362254E-2</v>
+        <v>4.9464821322507319E-2</v>
       </c>
       <c r="AH14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AH$9))</f>
-        <v>4.9914936543659902E-2</v>
+        <v>4.9602216169558261E-2</v>
       </c>
       <c r="AI14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AI$9))</f>
-        <v>4.9942942162081991E-2</v>
+        <v>4.9704589339490207E-2</v>
       </c>
       <c r="AJ14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AJ$9))</f>
-        <v>4.9961735849835175E-2</v>
+        <v>4.9780754720870554E-2</v>
       </c>
       <c r="AK14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AK$9))</f>
-        <v>4.9974343066903758E-2</v>
+        <v>4.9837359055491817E-2</v>
       </c>
       <c r="AL14">
         <f>IF($G14="s-curve",$E14+($F14-$E14)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E14:$F14,$E$9:$F$9,AL$9))</f>
-        <v>4.9982798179070587E-2</v>
+        <v>4.9879391575460584E-2</v>
       </c>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
@@ -64529,119 +64535,119 @@
       </c>
       <c r="J17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,J$9))</f>
-        <v>0.22583637175876042</v>
+        <v>0.2579411882892142</v>
       </c>
       <c r="K17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,K$9))</f>
-        <v>0.23794069854205344</v>
+        <v>0.27627957191928759</v>
       </c>
       <c r="L17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,L$9))</f>
-        <v>0.25531073627467749</v>
+        <v>0.2996426865499332</v>
       </c>
       <c r="M17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,M$9))</f>
-        <v>0.27980039129574813</v>
+        <v>0.32888715966126825</v>
       </c>
       <c r="N17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,N$9))</f>
-        <v>0.31348085192039021</v>
+        <v>0.36469629744075793</v>
       </c>
       <c r="O17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,O$9))</f>
-        <v>0.35825288915313458</v>
+        <v>0.40738008065427683</v>
       </c>
       <c r="P17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,P$9))</f>
-        <v>0.41515313709599611</v>
+        <v>0.45665704065968565</v>
       </c>
       <c r="Q17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Q$9))</f>
-        <v>0.48347495501936366</v>
+        <v>0.51148861284062241</v>
       </c>
       <c r="R17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,R$9))</f>
-        <v>0.56013280215001782</v>
+        <v>0.57005612372500036</v>
       </c>
       <c r="S17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,S$9))</f>
-        <v>0.63986719784998236</v>
+        <v>0.62994387627499959</v>
       </c>
       <c r="T17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,T$9))</f>
-        <v>0.71652504498063641</v>
+        <v>0.68851138715937765</v>
       </c>
       <c r="U17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,U$9))</f>
-        <v>0.78484686290400396</v>
+        <v>0.74334295934031447</v>
       </c>
       <c r="V17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,V$9))</f>
-        <v>0.84174711084686549</v>
+        <v>0.79261991934572329</v>
       </c>
       <c r="W17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,W$9))</f>
-        <v>0.88651914807960996</v>
+        <v>0.83530370255924202</v>
       </c>
       <c r="X17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,X$9))</f>
-        <v>0.92019960870425188</v>
+        <v>0.87111284033873182</v>
       </c>
       <c r="Y17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Y$9))</f>
-        <v>0.94468926372532258</v>
+        <v>0.90035731345006687</v>
       </c>
       <c r="Z17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,Z$9))</f>
-        <v>0.9620593014579466</v>
+        <v>0.92372042808071253</v>
       </c>
       <c r="AA17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AA$9))</f>
-        <v>0.97416362824123981</v>
+        <v>0.94205881171078576</v>
       </c>
       <c r="AB17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AB$9))</f>
-        <v>0.98249498325109563</v>
+        <v>0.95625494622724738</v>
       </c>
       <c r="AC17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AC$9))</f>
-        <v>0.98818077464538168</v>
+        <v>0.96712697743962805</v>
       </c>
       <c r="AD17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AD$9))</f>
-        <v>0.9920385585064766</v>
+        <v>0.97538491251428172</v>
       </c>
       <c r="AE17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AE$9))</f>
-        <v>0.99464571926057221</v>
+        <v>0.98161810407197958</v>
       </c>
       <c r="AF17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AF$9))</f>
-        <v>0.99640298147124717</v>
+        <v>0.98630077334741784</v>
       </c>
       <c r="AG17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AG$9))</f>
-        <v>0.99758526694023342</v>
+        <v>0.98980612042871075</v>
       </c>
       <c r="AH17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AH$9))</f>
-        <v>0.99837974368876004</v>
+        <v>0.99242316513444306</v>
       </c>
       <c r="AI17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AI$9))</f>
-        <v>0.99891318403965701</v>
+        <v>0.99437313027600394</v>
       </c>
       <c r="AJ17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AJ$9))</f>
-        <v>0.99927115904447961</v>
+        <v>0.99582389944515337</v>
       </c>
       <c r="AK17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AK$9))</f>
-        <v>0.99951129651245263</v>
+        <v>0.99690207724746327</v>
       </c>
       <c r="AL17">
         <f>IF($G17="s-curve",$E17+($F17-$E17)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E17:$F17,$E$9:$F$9,AL$9))</f>
-        <v>0.99967234626801127</v>
+        <v>0.99770269667543965</v>
       </c>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
@@ -65497,115 +65503,115 @@
       </c>
       <c r="K24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:K$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,K$9))</f>
-        <v>0.60875250837445216</v>
+        <v>0.62187252688637629</v>
       </c>
       <c r="L24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:L$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,L$9))</f>
-        <v>0.61291818587938018</v>
+        <v>0.6289705941446071</v>
       </c>
       <c r="M24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:M$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,M$9))</f>
-        <v>0.61897034927102668</v>
+        <v>0.63813978595964382</v>
       </c>
       <c r="N24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:N$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,N$9))</f>
-        <v>0.62765536813733869</v>
+        <v>0.64982134327496655</v>
       </c>
       <c r="O24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:O$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,O$9))</f>
-        <v>0.63990019564787404</v>
+        <v>0.66444357983063407</v>
       </c>
       <c r="P24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:P$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,P$9))</f>
-        <v>0.65674042596019511</v>
+        <v>0.68234814872037897</v>
       </c>
       <c r="Q24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Q$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Q$9))</f>
-        <v>0.67912644457656723</v>
+        <v>0.70369004032713844</v>
       </c>
       <c r="R24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:R$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,R$9))</f>
-        <v>0.707576568547998</v>
+        <v>0.72832852032984285</v>
       </c>
       <c r="S24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:S$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,S$9))</f>
-        <v>0.74173747750968178</v>
+        <v>0.75574430642031121</v>
       </c>
       <c r="T24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:T$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,T$9))</f>
-        <v>0.78006640107500891</v>
+        <v>0.78502806186250018</v>
       </c>
       <c r="U24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:U$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,U$9))</f>
-        <v>0.81993359892499118</v>
+        <v>0.8149719381374998</v>
       </c>
       <c r="V24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:V$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,V$9))</f>
-        <v>0.8582625224903182</v>
+        <v>0.84425569357968877</v>
       </c>
       <c r="W24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:W$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,W$9))</f>
-        <v>0.89242343145200187</v>
+        <v>0.87167147967015723</v>
       </c>
       <c r="X24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:X$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,X$9))</f>
-        <v>0.92087355542343274</v>
+        <v>0.89630995967286164</v>
       </c>
       <c r="Y24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Y$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Y$9))</f>
-        <v>0.94325957403980487</v>
+        <v>0.91765185127962101</v>
       </c>
       <c r="Z24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:Z$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,Z$9))</f>
-        <v>0.96009980435212594</v>
+        <v>0.93555642016936591</v>
       </c>
       <c r="AA24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AA$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AA$9))</f>
-        <v>0.97234463186266129</v>
+        <v>0.95017865672503343</v>
       </c>
       <c r="AB24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AB$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AB$9))</f>
-        <v>0.9810296507289733</v>
+        <v>0.96186021404035627</v>
       </c>
       <c r="AC24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AC$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AC$9))</f>
-        <v>0.9870818141206199</v>
+        <v>0.97102940585539288</v>
       </c>
       <c r="AD24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AD$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AD$9))</f>
-        <v>0.99124749162554782</v>
+        <v>0.97812747311362369</v>
       </c>
       <c r="AE24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AE$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AE$9))</f>
-        <v>0.99409038732269073</v>
+        <v>0.98356348871981403</v>
       </c>
       <c r="AF24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AF$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AF$9))</f>
-        <v>0.9960192792532383</v>
+        <v>0.98769245625714075</v>
       </c>
       <c r="AG24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AG$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AG$9))</f>
-        <v>0.99732285963028611</v>
+        <v>0.99080905203598979</v>
       </c>
       <c r="AH24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AH$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AH$9))</f>
-        <v>0.99820149073562359</v>
+        <v>0.99315038667370892</v>
       </c>
       <c r="AI24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AI$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AI$9))</f>
-        <v>0.99879263347011671</v>
+        <v>0.99490306021435537</v>
       </c>
       <c r="AJ24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AJ$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AJ$9))</f>
-        <v>0.99918987184438002</v>
+        <v>0.99621158256722153</v>
       </c>
       <c r="AK24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AK$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AK$9))</f>
-        <v>0.99945659201982839</v>
+        <v>0.99718656513800186</v>
       </c>
       <c r="AL24">
         <f>IF($G24="s-curve",$E24+($F24-$E24)*$O$2/(1+EXP($O$3*(COUNT($K$9:AL$9)+$O$4))),TREND($E24:$F24,$E$9:$F$9,AL$9))</f>
-        <v>0.9996355795222398</v>
+        <v>0.99791194972257657</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
@@ -73141,119 +73147,119 @@
       </c>
       <c r="J80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:J$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,J$9))</f>
-        <v>3.2295464698450495E-2</v>
+        <v>7.2426485361517731E-2</v>
       </c>
       <c r="K80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:K$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,K$9))</f>
-        <v>4.7425873177566781E-2</v>
+        <v>9.534946489910949E-2</v>
       </c>
       <c r="L80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:L$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,L$9))</f>
-        <v>6.9138420343346815E-2</v>
+        <v>0.12455335818741645</v>
       </c>
       <c r="M80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:M$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,M$9))</f>
-        <v>9.9750489119685135E-2</v>
+        <v>0.16110894957658525</v>
       </c>
       <c r="N80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:N$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,N$9))</f>
-        <v>0.14185106490048777</v>
+        <v>0.20587037180094736</v>
       </c>
       <c r="O80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:O$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,O$9))</f>
-        <v>0.19781611144141822</v>
+        <v>0.259225100817846</v>
       </c>
       <c r="P80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:P$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,P$9))</f>
-        <v>0.2689414213699951</v>
+        <v>0.32082130082460703</v>
       </c>
       <c r="Q80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Q$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Q$9))</f>
-        <v>0.35434369377420455</v>
+        <v>0.38936076605077802</v>
       </c>
       <c r="R80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:R$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,R$9))</f>
-        <v>0.45016600268752216</v>
+        <v>0.46257015465625045</v>
       </c>
       <c r="S80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:S$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,S$9))</f>
-        <v>0.54983399731247795</v>
+        <v>0.5374298453437496</v>
       </c>
       <c r="T80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:T$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,T$9))</f>
-        <v>0.6456563062257954</v>
+        <v>0.61063923394922204</v>
       </c>
       <c r="U80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:U$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,U$9))</f>
-        <v>0.7310585786300049</v>
+        <v>0.67917869917539297</v>
       </c>
       <c r="V80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:V$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,V$9))</f>
-        <v>0.8021838885585818</v>
+        <v>0.740774899182154</v>
       </c>
       <c r="W80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:W$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,W$9))</f>
-        <v>0.85814893509951229</v>
+        <v>0.79412962819905253</v>
       </c>
       <c r="X80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:X$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,X$9))</f>
-        <v>0.9002495108803148</v>
+        <v>0.83889105042341472</v>
       </c>
       <c r="Y80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Y$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Y$9))</f>
-        <v>0.93086157965665328</v>
+        <v>0.87544664181258358</v>
       </c>
       <c r="Z80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:Z$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,Z$9))</f>
-        <v>0.95257412682243336</v>
+        <v>0.90465053510089055</v>
       </c>
       <c r="AA80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AA$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AA$9))</f>
-        <v>0.96770453530154954</v>
+        <v>0.92757351463848225</v>
       </c>
       <c r="AB80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AB$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AB$9))</f>
-        <v>0.97811872906386943</v>
+        <v>0.94531868278405917</v>
       </c>
       <c r="AC80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AC$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AC$9))</f>
-        <v>0.98522596830672693</v>
+        <v>0.95890872179953501</v>
       </c>
       <c r="AD80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AD$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AD$9))</f>
-        <v>0.99004819813309575</v>
+        <v>0.96923114064285198</v>
       </c>
       <c r="AE80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AE$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AE$9))</f>
-        <v>0.99330714907571527</v>
+        <v>0.97702263008997436</v>
       </c>
       <c r="AF80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AF$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AF$9))</f>
-        <v>0.99550372683905886</v>
+        <v>0.98287596668427235</v>
       </c>
       <c r="AG80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AG$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AG$9))</f>
-        <v>0.99698158367529166</v>
+        <v>0.98725765053588843</v>
       </c>
       <c r="AH80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AH$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AH$9))</f>
-        <v>0.9979746796109501</v>
+        <v>0.99052895641805383</v>
       </c>
       <c r="AI80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AI$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AI$9))</f>
-        <v>0.9986414800495711</v>
+        <v>0.99296641284500486</v>
       </c>
       <c r="AJ80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AJ$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AJ$9))</f>
-        <v>0.9990889488055994</v>
+        <v>0.99477987430644166</v>
       </c>
       <c r="AK80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AK$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AK$9))</f>
-        <v>0.99938912064056562</v>
+        <v>0.99612759655932892</v>
       </c>
       <c r="AL80">
         <f>IF($G80="s-curve",$E80+($F80-$E80)*$O$2/(1+EXP($O$3*(COUNT($I$9:AL$9)+$O$4))),TREND($E80:$F80,$E$9:$F$9,AL$9))</f>
-        <v>0.99959043283501392</v>
+        <v>0.99712837084429951</v>
       </c>
     </row>
     <row r="81" spans="1:38" x14ac:dyDescent="0.25">
